--- a/data/export/2026-10-28-operations.xlsx
+++ b/data/export/2026-10-28-operations.xlsx
@@ -427,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -442,7 +442,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
     <col width="26" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
@@ -676,7 +676,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>06:12</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
@@ -726,7 +726,7 @@
       <c r="AC2" s="2" t="inlineStr"/>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -759,32 +759,36 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -792,7 +796,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -816,17 +820,17 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -836,13 +840,17 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC3" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC3" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -908,7 +916,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>06:12</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -947,7 +955,7 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
@@ -958,7 +966,7 @@
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -991,32 +999,36 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:58</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1024,7 +1036,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1048,17 +1060,17 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1068,13 +1080,17 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC5" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1156,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1179,7 +1195,7 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
@@ -1190,7 +1206,7 @@
       <c r="AC6" s="2" t="inlineStr"/>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1272,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1306,7 +1322,7 @@
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1388,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1422,7 +1438,7 @@
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1504,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1538,7 +1554,7 @@
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1551,22 +1567,22 @@
       <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>沪A32298D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1599,12 +1615,12 @@
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1618,7 +1634,7 @@
       <c r="U10" s="2" t="inlineStr"/>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1654,35 +1670,35 @@
       <c r="AC10" s="2" t="inlineStr"/>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1715,12 +1731,12 @@
       <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1734,7 +1750,7 @@
       <c r="U11" s="2" t="inlineStr"/>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1770,35 +1786,35 @@
       <c r="AC11" s="2" t="inlineStr"/>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1831,12 +1847,12 @@
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1850,7 +1866,7 @@
       <c r="U12" s="2" t="inlineStr"/>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1886,35 +1902,35 @@
       <c r="AC12" s="2" t="inlineStr"/>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1947,12 +1963,12 @@
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1966,7 +1982,7 @@
       <c r="U13" s="2" t="inlineStr"/>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1991,7 +2007,7 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
@@ -2002,35 +2018,35 @@
       <c r="AC13" s="2" t="inlineStr"/>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2063,12 +2079,12 @@
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2082,7 +2098,7 @@
       <c r="U14" s="2" t="inlineStr"/>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2118,35 +2134,35 @@
       <c r="AC14" s="2" t="inlineStr"/>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>沪A72305D</t>
+          <t>沪A12050A</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2179,12 +2195,12 @@
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2198,7 +2214,7 @@
       <c r="U15" s="2" t="inlineStr"/>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -2234,35 +2250,35 @@
       <c r="AC15" s="2" t="inlineStr"/>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2295,12 +2311,12 @@
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2314,7 +2330,7 @@
       <c r="U16" s="2" t="inlineStr"/>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2339,7 +2355,7 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
@@ -2350,35 +2366,35 @@
       <c r="AC16" s="2" t="inlineStr"/>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2411,12 +2427,12 @@
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2430,7 +2446,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2455,7 +2471,7 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
@@ -2466,7 +2482,7 @@
       <c r="AC17" s="2" t="inlineStr"/>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -2479,22 +2495,22 @@
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2527,12 +2543,12 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2546,7 +2562,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2582,25 +2598,25 @@
       <c r="AC18" s="2" t="inlineStr"/>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2610,7 +2626,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2648,7 +2664,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2698,35 +2714,35 @@
       <c r="AC19" s="2" t="inlineStr"/>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2764,7 +2780,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2778,7 +2794,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2814,35 +2830,35 @@
       <c r="AC20" s="2" t="inlineStr"/>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A30829D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2880,7 +2896,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2894,7 +2910,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2930,35 +2946,35 @@
       <c r="AC21" s="2" t="inlineStr"/>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A30260D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2991,12 +3007,12 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3010,7 +3026,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3046,7 +3062,3487 @@
       <c r="AC22" s="2" t="inlineStr"/>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AD23" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AD24" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr"/>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AD25" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AD26" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AD27" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr"/>
+      <c r="AD28" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AD29" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AD30" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr"/>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AD31" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AD32" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AD33" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr"/>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AD34" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr"/>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AD35" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr"/>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AD36" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr"/>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AD37" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AD38" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr"/>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>沪A30829D</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AD39" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr"/>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr"/>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr"/>
+      <c r="AD40" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr"/>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>沪A30260D</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr"/>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr"/>
+      <c r="AD41" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr"/>
+      <c r="AD42" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr"/>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr"/>
+      <c r="AD43" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr"/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>沪A51582D</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr"/>
+      <c r="AD44" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr"/>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr"/>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr"/>
+      <c r="AD45" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr"/>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>沪A35683D</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr"/>
+      <c r="AD46" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr"/>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr"/>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr"/>
+      <c r="AD47" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr"/>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr"/>
+      <c r="AD48" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr"/>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr"/>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr"/>
+      <c r="AD49" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr"/>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>沪A53062D</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr"/>
+      <c r="AD50" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr"/>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr"/>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr"/>
+      <c r="AD51" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr"/>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr"/>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr"/>
+      <c r="AD52" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-28-operations.xlsx
+++ b/data/export/2026-10-28-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD52"/>
+  <dimension ref="A1:AD80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -437,7 +437,7 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
@@ -450,7 +450,7 @@
     <col width="10" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
     <col width="20" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="36" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
@@ -643,32 +643,36 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:33</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -676,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -700,17 +704,17 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -720,13 +724,17 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC2" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -796,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -835,14 +843,14 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
           <t>74.0</t>
@@ -850,7 +858,7 @@
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -883,32 +891,36 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:37</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -916,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -940,17 +952,17 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -960,13 +972,17 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC4" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1009,24 +1025,24 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>98分钟</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -1036,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1075,22 +1091,22 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1123,32 +1139,36 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1156,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1180,17 +1200,17 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1200,13 +1220,17 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1239,32 +1263,36 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -1272,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1296,33 +1324,37 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1355,32 +1387,36 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1388,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1412,33 +1448,37 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1471,32 +1511,36 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
           <t>06:22</t>
@@ -1504,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1528,33 +1572,37 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1668,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1659,7 +1707,7 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
@@ -1670,7 +1718,7 @@
       <c r="AC10" s="2" t="inlineStr"/>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1784,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1775,7 +1823,7 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
@@ -1786,7 +1834,7 @@
       <c r="AC11" s="2" t="inlineStr"/>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1852,7 +1900,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1902,7 +1950,7 @@
       <c r="AC12" s="2" t="inlineStr"/>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1968,7 +2016,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2012,13 +2060,17 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC13" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2136,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2134,7 +2186,7 @@
       <c r="AC14" s="2" t="inlineStr"/>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2252,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2250,7 +2302,7 @@
       <c r="AC15" s="2" t="inlineStr"/>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2368,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2360,13 +2412,17 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC16" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2379,22 +2435,22 @@
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A67026D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2432,7 +2488,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2446,7 +2502,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2476,41 +2532,45 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC17" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A02126A</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2543,12 +2603,12 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2562,7 +2622,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2598,35 +2658,35 @@
       <c r="AC18" s="2" t="inlineStr"/>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2659,12 +2719,12 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2678,7 +2738,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2703,46 +2763,50 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2775,12 +2839,12 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2794,7 +2858,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2819,46 +2883,50 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2891,12 +2959,12 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:12</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2910,7 +2978,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2935,46 +3003,50 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A72305D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3007,12 +3079,12 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3026,7 +3098,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3051,46 +3123,50 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A08953A</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3123,12 +3199,12 @@
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3142,7 +3218,7 @@
       <c r="U23" s="2" t="inlineStr"/>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3167,46 +3243,50 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3239,12 +3319,12 @@
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3258,7 +3338,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3283,7 +3363,7 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
@@ -3294,35 +3374,35 @@
       <c r="AC24" s="2" t="inlineStr"/>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3355,12 +3435,12 @@
       <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3374,7 +3454,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3399,7 +3479,7 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
@@ -3410,7 +3490,7 @@
       <c r="AC25" s="2" t="inlineStr"/>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -3423,60 +3503,64 @@
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3490,7 +3574,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3500,33 +3584,37 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -3539,7 +3627,7 @@
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3549,7 +3637,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3587,12 +3675,12 @@
       <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3606,7 +3694,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3631,7 +3719,7 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
@@ -3642,7 +3730,7 @@
       <c r="AC27" s="2" t="inlineStr"/>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -3655,7 +3743,7 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -3665,7 +3753,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -3703,12 +3791,12 @@
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3722,7 +3810,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3758,7 +3846,7 @@
       <c r="AC28" s="2" t="inlineStr"/>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -3771,22 +3859,22 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3819,12 +3907,12 @@
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3838,7 +3926,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3863,7 +3951,7 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
@@ -3874,7 +3962,7 @@
       <c r="AC29" s="2" t="inlineStr"/>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -3887,32 +3975,32 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程38%处后消失；随后反向物理轨迹由seq28推进至seq40，推进12站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -3935,12 +4023,12 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3948,13 +4036,21 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>白桦路明月路</t>
+        </is>
+      </c>
       <c r="S30" s="2" t="inlineStr"/>
       <c r="T30" s="2" t="inlineStr"/>
-      <c r="U30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq25映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -3990,7 +4086,7 @@
       <c r="AC30" s="2" t="inlineStr"/>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4003,22 +4099,22 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>07:24</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -4051,12 +4147,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4070,7 +4166,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4106,7 +4202,7 @@
       <c r="AC31" s="2" t="inlineStr"/>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4119,22 +4215,22 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -4167,12 +4263,12 @@
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4186,7 +4282,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4222,7 +4318,7 @@
       <c r="AC32" s="2" t="inlineStr"/>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4235,22 +4331,22 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4283,12 +4379,12 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4302,7 +4398,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4338,7 +4434,7 @@
       <c r="AC33" s="2" t="inlineStr"/>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4351,22 +4447,22 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4399,12 +4495,12 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4418,7 +4514,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4454,7 +4550,7 @@
       <c r="AC34" s="2" t="inlineStr"/>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4467,7 +4563,7 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -4477,7 +4573,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -4515,12 +4611,12 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4534,7 +4630,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4570,7 +4666,7 @@
       <c r="AC35" s="2" t="inlineStr"/>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4583,7 +4679,7 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -4593,7 +4689,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -4631,12 +4727,12 @@
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4650,7 +4746,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4686,35 +4782,35 @@
       <c r="AC36" s="2" t="inlineStr"/>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4747,12 +4843,12 @@
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4766,7 +4862,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4791,7 +4887,7 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
@@ -4802,35 +4898,35 @@
       <c r="AC37" s="2" t="inlineStr"/>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4863,12 +4959,12 @@
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4882,7 +4978,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -4918,35 +5014,35 @@
       <c r="AC38" s="2" t="inlineStr"/>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A30829D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4979,12 +5075,12 @@
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4998,7 +5094,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5034,35 +5130,35 @@
       <c r="AC39" s="2" t="inlineStr"/>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -5095,12 +5191,12 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5114,7 +5210,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5150,35 +5246,35 @@
       <c r="AC40" s="2" t="inlineStr"/>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A30260D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -5211,12 +5307,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5230,7 +5326,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5266,35 +5362,35 @@
       <c r="AC41" s="2" t="inlineStr"/>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5327,12 +5423,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5346,7 +5442,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5382,35 +5478,35 @@
       <c r="AC42" s="2" t="inlineStr"/>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5443,12 +5539,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5462,7 +5558,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5498,35 +5594,35 @@
       <c r="AC43" s="2" t="inlineStr"/>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A51582D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5559,12 +5655,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5578,7 +5674,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5614,35 +5710,35 @@
       <c r="AC44" s="2" t="inlineStr"/>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5675,12 +5771,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5694,7 +5790,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5730,35 +5826,35 @@
       <c r="AC45" s="2" t="inlineStr"/>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A35683D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5796,7 +5892,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5810,7 +5906,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5846,35 +5942,35 @@
       <c r="AC46" s="2" t="inlineStr"/>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5907,12 +6003,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5926,7 +6022,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -5962,35 +6058,35 @@
       <c r="AC47" s="2" t="inlineStr"/>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -6023,12 +6119,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6042,7 +6138,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6078,35 +6174,35 @@
       <c r="AC48" s="2" t="inlineStr"/>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -6139,12 +6235,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6158,7 +6254,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6194,35 +6290,35 @@
       <c r="AC49" s="2" t="inlineStr"/>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A53062D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -6255,12 +6351,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6274,7 +6370,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6310,35 +6406,35 @@
       <c r="AC50" s="2" t="inlineStr"/>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A50235D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>07:47</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6376,7 +6472,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6390,7 +6486,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>07:47</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6426,35 +6522,35 @@
       <c r="AC51" s="2" t="inlineStr"/>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6487,12 +6583,12 @@
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6506,7 +6602,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6531,7 +6627,7 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
@@ -6542,7 +6638,3295 @@
       <c r="AC52" s="2" t="inlineStr"/>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr"/>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr"/>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr"/>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr"/>
+      <c r="AD53" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr"/>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr"/>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
+      <c r="AD54" s="2" t="inlineStr">
+        <is>
+          <t>1/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr"/>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr"/>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr"/>
+      <c r="AD55" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr"/>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr"/>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr"/>
+      <c r="AD56" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr"/>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr"/>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr"/>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr"/>
+      <c r="AD57" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr"/>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>沪A30829D</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr"/>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr"/>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr"/>
+      <c r="AD58" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr"/>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>91分钟</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr"/>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AD59" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr"/>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>沪A30260D</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr"/>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr"/>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr"/>
+      <c r="AD60" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr"/>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>92分钟</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr"/>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AD61" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr"/>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>93分钟</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr"/>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AD62" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr"/>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>沪A51582D</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr"/>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr"/>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr"/>
+      <c r="AD63" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr"/>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr"/>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr"/>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr"/>
+      <c r="AD64" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr"/>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>沪A35683D</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr"/>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr"/>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr"/>
+      <c r="AD65" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr"/>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr"/>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr"/>
+      <c r="AD66" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr"/>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr"/>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr"/>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr"/>
+      <c r="AD67" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr"/>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr"/>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr"/>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr"/>
+      <c r="AD68" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr"/>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>沪A53062D</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr"/>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr"/>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr"/>
+      <c r="AD69" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr"/>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr"/>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr"/>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr"/>
+      <c r="AD70" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr"/>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr"/>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr"/>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr"/>
+      <c r="AD71" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr"/>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr"/>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr"/>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr"/>
+      <c r="AD72" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr"/>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>沪A53893D</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr"/>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr"/>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr"/>
+      <c r="AD73" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr"/>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr"/>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr"/>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AD74" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr"/>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr"/>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr"/>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr"/>
+      <c r="AD75" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr"/>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr"/>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr"/>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr"/>
+      <c r="AD76" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr"/>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr"/>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr"/>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AD77" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr"/>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>沪A30829D</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr"/>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr"/>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr"/>
+      <c r="AD78" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr"/>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr"/>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr"/>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AD79" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr"/>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>沪A35683D</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr"/>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr"/>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr"/>
+      <c r="AD80" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-28-operations.xlsx
+++ b/data/export/2026-10-28-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD80"/>
+  <dimension ref="A1:AD99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -719,22 +719,22 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1751,32 +1751,36 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1784,7 +1788,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1808,17 +1812,17 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1828,13 +1832,17 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC11" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1908,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1939,7 +1947,7 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
@@ -1983,32 +1991,36 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2016,7 +2028,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2040,37 +2052,37 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2148,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2175,7 +2187,7 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
@@ -2252,7 +2264,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2291,7 +2303,7 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
@@ -2368,7 +2380,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2407,7 +2419,7 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
@@ -2488,7 +2500,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2608,7 +2620,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2724,7 +2736,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2763,7 +2775,7 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
@@ -2844,7 +2856,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2964,7 +2976,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3084,7 +3096,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3138,7 +3150,7 @@
       </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3204,7 +3216,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3324,7 +3336,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3368,13 +3380,17 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC24" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3440,7 +3456,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3497,70 +3513,66 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3574,7 +3586,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3584,17 +3596,17 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3604,45 +3616,41 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC26" s="2" t="inlineStr">
-        <is>
-          <t>135.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr"/>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3675,12 +3683,12 @@
       <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3694,7 +3702,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3719,46 +3727,50 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>92.5</t>
+        </is>
+      </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3791,12 +3803,12 @@
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3810,7 +3822,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3835,7 +3847,7 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
@@ -3846,35 +3858,35 @@
       <c r="AC28" s="2" t="inlineStr"/>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A12050A</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3907,12 +3919,12 @@
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3926,7 +3938,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3962,45 +3974,45 @@
       <c r="AC29" s="2" t="inlineStr"/>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A72305D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>疑似区间车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程38%处后消失；随后反向物理轨迹由seq28推进至seq40，推进12站，达到≥2站确认条件</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -4023,12 +4035,12 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4036,21 +4048,13 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>白桦路明月路</t>
-        </is>
-      </c>
+      <c r="R30" s="2" t="inlineStr"/>
       <c r="S30" s="2" t="inlineStr"/>
       <c r="T30" s="2" t="inlineStr"/>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>区间折返已由主分类器确认；折返点按重建物理位置seq25映射；现有采样不足以把折返发车时间控制在±10分钟</t>
-        </is>
-      </c>
+      <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4075,46 +4079,50 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -4147,12 +4155,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4166,7 +4174,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4191,18 +4199,22 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -4215,52 +4227,56 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>06:42</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4268,7 +4284,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4282,7 +4298,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4292,33 +4308,37 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -4331,22 +4351,22 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4379,12 +4399,12 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4398,7 +4418,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4423,7 +4443,7 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
@@ -4447,60 +4467,64 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>06:26</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4514,7 +4538,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4524,33 +4548,37 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -4563,7 +4591,7 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -4573,7 +4601,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -4611,12 +4639,12 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4630,7 +4658,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4655,7 +4683,7 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
@@ -4679,7 +4707,7 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -4689,7 +4717,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -4699,12 +4727,12 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程38%处后消失；随后反向物理轨迹由seq28推进至seq60，推进32站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -4727,12 +4755,12 @@
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4740,13 +4768,21 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>白桦路明月路</t>
+        </is>
+      </c>
       <c r="S36" s="2" t="inlineStr"/>
       <c r="T36" s="2" t="inlineStr"/>
-      <c r="U36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq25映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4771,7 +4807,7 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
@@ -4795,7 +4831,7 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -4805,7 +4841,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -4815,40 +4851,44 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>154分钟</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4862,7 +4902,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4872,33 +4912,37 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>154.0</t>
+        </is>
+      </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -4911,7 +4955,7 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -4921,7 +4965,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -4959,12 +5003,12 @@
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4978,7 +5022,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5003,7 +5047,7 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
@@ -5027,22 +5071,22 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>07:24</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -5075,12 +5119,12 @@
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5094,7 +5138,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5119,7 +5163,7 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
@@ -5143,22 +5187,22 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -5191,12 +5235,12 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5210,7 +5254,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5259,7 +5303,7 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -5269,7 +5313,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -5307,12 +5351,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5326,7 +5370,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5375,7 +5419,7 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -5385,7 +5429,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -5423,12 +5467,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5442,7 +5486,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5491,22 +5535,22 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5539,12 +5583,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5558,7 +5602,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5607,7 +5651,7 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -5617,7 +5661,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -5655,12 +5699,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5674,7 +5718,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5723,32 +5767,32 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程19%处后消失；随后反向物理轨迹由seq37推进至seq41，推进4站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -5771,12 +5815,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5784,13 +5828,25 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R45" s="2" t="inlineStr"/>
-      <c r="S45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t>川周公路康沈路</t>
+        </is>
+      </c>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
       <c r="T45" s="2" t="inlineStr"/>
-      <c r="U45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq13映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5839,7 +5895,7 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -5849,7 +5905,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -5887,12 +5943,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5906,7 +5962,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5955,7 +6011,7 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -5965,7 +6021,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -6003,12 +6059,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6022,7 +6078,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6071,22 +6127,22 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -6119,12 +6175,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6138,7 +6194,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6187,22 +6243,22 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -6235,12 +6291,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6254,7 +6310,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6303,7 +6359,7 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -6313,7 +6369,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -6351,12 +6407,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6370,7 +6426,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6419,7 +6475,7 @@
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -6429,7 +6485,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -6467,12 +6523,12 @@
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6486,7 +6542,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6535,22 +6591,22 @@
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6583,12 +6639,12 @@
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6602,7 +6658,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6651,22 +6707,22 @@
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>08:52</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6704,7 +6760,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6718,7 +6774,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6743,7 +6799,7 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
@@ -6767,7 +6823,7 @@
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -6777,7 +6833,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -6815,12 +6871,12 @@
       <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6834,7 +6890,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6859,22 +6915,18 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC54" s="2" t="inlineStr">
-        <is>
-          <t>135.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr"/>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -6887,7 +6939,7 @@
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -6897,7 +6949,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -6940,7 +6992,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6954,7 +7006,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -6979,7 +7031,7 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
@@ -6997,28 +7049,28 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -7056,7 +7108,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7070,7 +7122,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -7095,7 +7147,7 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
@@ -7106,35 +7158,35 @@
       <c r="AC56" s="2" t="inlineStr"/>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -7172,7 +7224,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7186,7 +7238,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7211,7 +7263,7 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
@@ -7222,35 +7274,35 @@
       <c r="AC57" s="2" t="inlineStr"/>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A30829D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -7283,12 +7335,12 @@
       <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7302,7 +7354,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7327,7 +7379,7 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
@@ -7338,77 +7390,73 @@
       <c r="AC58" s="2" t="inlineStr"/>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr"/>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N59" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7422,7 +7470,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7432,17 +7480,17 @@
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7452,45 +7500,41 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC59" s="2" t="inlineStr">
-        <is>
-          <t>91.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr"/>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A30260D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7523,12 +7567,12 @@
       <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7542,7 +7586,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7567,88 +7611,88 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB60" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC60" s="2" t="inlineStr"/>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr"/>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N61" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7662,7 +7706,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7672,17 +7716,17 @@
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
@@ -7697,82 +7741,78 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>93分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr"/>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N62" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7786,7 +7826,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -7796,17 +7836,17 @@
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
@@ -7816,45 +7856,41 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC62" s="2" t="inlineStr">
-        <is>
-          <t>93.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr"/>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A51582D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7887,12 +7923,12 @@
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7906,7 +7942,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -7931,7 +7967,7 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
@@ -7942,35 +7978,35 @@
       <c r="AC63" s="2" t="inlineStr"/>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -8003,12 +8039,12 @@
       <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8022,7 +8058,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -8047,46 +8083,50 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB64" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC64" s="2" t="inlineStr"/>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>154.0</t>
+        </is>
+      </c>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A35683D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -8119,12 +8159,12 @@
       <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8138,7 +8178,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8174,35 +8214,35 @@
       <c r="AC65" s="2" t="inlineStr"/>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -8235,12 +8275,12 @@
       <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8254,7 +8294,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8279,7 +8319,7 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
@@ -8290,7 +8330,7 @@
       <c r="AC66" s="2" t="inlineStr"/>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8343,7 @@
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -8313,7 +8353,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -8351,12 +8391,12 @@
       <c r="N67" s="2" t="inlineStr"/>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8370,7 +8410,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8395,7 +8435,7 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
@@ -8419,22 +8459,22 @@
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -8467,12 +8507,12 @@
       <c r="N68" s="2" t="inlineStr"/>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8486,7 +8526,7 @@
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
@@ -8511,7 +8551,7 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
@@ -8535,7 +8575,7 @@
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A53062D</t>
+          <t>沪A30829D</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -8545,7 +8585,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -8583,12 +8623,12 @@
       <c r="N69" s="2" t="inlineStr"/>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8602,7 +8642,7 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
@@ -8627,7 +8667,7 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
@@ -8651,7 +8691,7 @@
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A50235D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -8661,7 +8701,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>07:47</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -8671,40 +8711,44 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr"/>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N70" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8718,7 +8762,7 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>07:47</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -8728,33 +8772,37 @@
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB70" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC70" s="2" t="inlineStr"/>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -8767,7 +8815,7 @@
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A30260D</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -8777,7 +8825,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -8815,12 +8863,12 @@
       <c r="N71" s="2" t="inlineStr"/>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8834,7 +8882,7 @@
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
@@ -8859,7 +8907,7 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
@@ -8883,7 +8931,7 @@
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -8893,7 +8941,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -8903,40 +8951,44 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr"/>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N72" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -8950,7 +9002,7 @@
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
@@ -8960,17 +9012,17 @@
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
@@ -8980,13 +9032,17 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC72" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -8999,60 +9055,64 @@
       <c r="B73" s="2" t="inlineStr"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>沪A53893D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr"/>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N73" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9066,7 +9126,7 @@
       <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
@@ -9076,33 +9136,37 @@
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB73" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC73" s="2" t="inlineStr"/>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
       <c r="AD73" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -9115,7 +9179,7 @@
       <c r="B74" s="2" t="inlineStr"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A51582D</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -9125,7 +9189,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -9168,7 +9232,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9182,7 +9246,7 @@
       <c r="U74" s="2" t="inlineStr"/>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
@@ -9212,17 +9276,13 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC74" s="2" t="inlineStr">
-        <is>
-          <t>91.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr"/>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -9235,60 +9295,64 @@
       <c r="B75" s="2" t="inlineStr"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>08:20</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>113分钟</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr"/>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N75" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9302,7 +9366,7 @@
       <c r="U75" s="2" t="inlineStr"/>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
@@ -9312,17 +9376,17 @@
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
@@ -9332,13 +9396,17 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC75" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>113.0</t>
+        </is>
+      </c>
       <c r="AD75" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -9351,7 +9419,7 @@
       <c r="B76" s="2" t="inlineStr"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>沪A36930D</t>
+          <t>沪A35683D</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -9361,7 +9429,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -9371,40 +9439,44 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr"/>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N76" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9418,7 +9490,7 @@
       <c r="U76" s="2" t="inlineStr"/>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
@@ -9428,33 +9500,37 @@
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB76" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC76" s="2" t="inlineStr"/>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AD76" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -9467,7 +9543,7 @@
       <c r="B77" s="2" t="inlineStr"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -9477,7 +9553,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -9515,12 +9591,12 @@
       <c r="N77" s="2" t="inlineStr"/>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9534,7 +9610,7 @@
       <c r="U77" s="2" t="inlineStr"/>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
@@ -9564,17 +9640,13 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC77" s="2" t="inlineStr">
-        <is>
-          <t>92.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr"/>
       <c r="AD77" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -9587,60 +9659,64 @@
       <c r="B78" s="2" t="inlineStr"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>沪A30829D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>08:35</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>106分钟</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr"/>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N78" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9654,7 +9730,7 @@
       <c r="U78" s="2" t="inlineStr"/>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
@@ -9664,17 +9740,17 @@
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
@@ -9684,13 +9760,17 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC78" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>106.0</t>
+        </is>
+      </c>
       <c r="AD78" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -9703,60 +9783,64 @@
       <c r="B79" s="2" t="inlineStr"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr"/>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N79" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -9770,7 +9854,7 @@
       <c r="U79" s="2" t="inlineStr"/>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W79" s="2" t="inlineStr">
@@ -9780,17 +9864,17 @@
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
@@ -9805,12 +9889,12 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AD79" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -9823,7 +9907,7 @@
       <c r="B80" s="2" t="inlineStr"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>沪A35683D</t>
+          <t>沪A53062D</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -9833,7 +9917,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -9843,40 +9927,44 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr"/>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N80" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -9890,41 +9978,2289 @@
       <c r="U80" s="2" t="inlineStr"/>
       <c r="V80" s="2" t="inlineStr">
         <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="AD80" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr"/>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>97分钟</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr"/>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="AD81" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr"/>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr"/>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr"/>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr"/>
+      <c r="AD82" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr"/>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr"/>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr"/>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr"/>
+      <c r="AD83" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr"/>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>沪A53893D</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr"/>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr"/>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr"/>
+      <c r="AD84" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr"/>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr"/>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr"/>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AD85" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr"/>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr"/>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr"/>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr"/>
+      <c r="AD86" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr"/>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr"/>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr"/>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr"/>
+      <c r="AD87" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr"/>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr"/>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr"/>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AD88" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr"/>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>沪A30829D</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr"/>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr"/>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr"/>
+      <c r="AD89" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr"/>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>沪A30260D</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr"/>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr"/>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr"/>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr"/>
+      <c r="AD90" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr"/>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr"/>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr"/>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AD91" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr"/>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>沪A51582D</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr"/>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr"/>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr"/>
+      <c r="AD92" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr"/>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>沪A35683D</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="W80" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr"/>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr"/>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr"/>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X80" s="2" t="inlineStr">
+      <c r="X93" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y80" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Z80" s="2" t="inlineStr">
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA80" s="2" t="inlineStr">
+      <c r="AA93" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB80" s="2" t="inlineStr">
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AD93" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr"/>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr"/>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr"/>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr"/>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>113.0</t>
+        </is>
+      </c>
+      <c r="AD94" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr"/>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr"/>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr"/>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="AD95" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr"/>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr"/>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr"/>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr"/>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AC80" s="2" t="inlineStr"/>
-      <c r="AD80" s="2" t="inlineStr">
+      <c r="AC96" s="2" t="inlineStr"/>
+      <c r="AD96" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr"/>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr"/>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr"/>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr"/>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>106.0</t>
+        </is>
+      </c>
+      <c r="AD97" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr"/>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr"/>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr"/>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr"/>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="AD98" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr"/>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr"/>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr"/>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr"/>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr"/>
+      <c r="AD99" s="2" t="inlineStr">
         <is>
           <t>—/18</t>
         </is>

--- a/data/export/2026-10-28-operations.xlsx
+++ b/data/export/2026-10-28-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD99"/>
+  <dimension ref="A1:AD102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2347,32 +2347,36 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2380,7 +2384,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2404,17 +2408,17 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2424,12 +2428,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
@@ -2736,7 +2740,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2856,7 +2860,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2976,7 +2980,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3096,7 +3100,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3336,7 +3340,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3688,7 +3692,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3808,7 +3812,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3924,7 +3928,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -4040,7 +4044,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4084,12 +4088,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AD30" s="2" t="inlineStr">
@@ -4160,7 +4164,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4284,7 +4288,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4404,7 +4408,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4524,7 +4528,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4644,7 +4648,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4760,7 +4764,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4888,7 +4892,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -5008,7 +5012,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5124,7 +5128,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5240,7 +5244,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5279,7 +5283,7 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
@@ -5472,7 +5476,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5511,7 +5515,7 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
@@ -5704,7 +5708,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5792,7 +5796,7 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程19%处后消失；随后反向物理轨迹由seq37推进至seq41，推进4站，达到≥2站确认条件</t>
+          <t>原方向在全程19%处后消失；随后反向物理轨迹由seq37推进至seq45，推进8站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -5820,7 +5824,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -6064,7 +6068,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6296,7 +6300,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6412,7 +6416,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6644,7 +6648,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6876,7 +6880,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6992,7 +6996,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7108,7 +7112,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7224,7 +7228,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7456,7 +7460,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7572,7 +7576,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7692,7 +7696,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7812,7 +7816,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7928,7 +7932,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8044,7 +8048,7 @@
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8164,7 +8168,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8280,7 +8284,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8337,28 +8341,28 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -8391,12 +8395,12 @@
       <c r="N67" s="2" t="inlineStr"/>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8410,7 +8414,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8446,35 +8450,35 @@
       <c r="AC67" s="2" t="inlineStr"/>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -8507,12 +8511,12 @@
       <c r="N68" s="2" t="inlineStr"/>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8526,7 +8530,7 @@
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
@@ -8551,7 +8555,7 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
@@ -8562,7 +8566,7 @@
       <c r="AC68" s="2" t="inlineStr"/>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -8575,7 +8579,7 @@
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A30829D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -8585,7 +8589,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -8628,7 +8632,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8642,7 +8646,7 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
@@ -8691,64 +8695,60 @@
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>06:40</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr"/>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N70" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr"/>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8762,7 +8762,7 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -8772,37 +8772,33 @@
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC70" s="2" t="inlineStr">
-        <is>
-          <t>91.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr"/>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -8815,7 +8811,7 @@
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>沪A30260D</t>
+          <t>沪A30829D</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -8825,7 +8821,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -8863,12 +8859,12 @@
       <c r="N71" s="2" t="inlineStr"/>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8882,7 +8878,7 @@
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
@@ -8931,7 +8927,7 @@
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -8941,7 +8937,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -8961,24 +8957,24 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr"/>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
@@ -9002,7 +8998,7 @@
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
@@ -9037,12 +9033,12 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -9055,64 +9051,60 @@
       <c r="B73" s="2" t="inlineStr"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A30260D</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>93分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr"/>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N73" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr"/>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9126,7 +9118,7 @@
       <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
@@ -9136,17 +9128,17 @@
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
@@ -9156,17 +9148,13 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC73" s="2" t="inlineStr">
-        <is>
-          <t>93.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr"/>
       <c r="AD73" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -9179,52 +9167,56 @@
       <c r="B74" s="2" t="inlineStr"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>沪A51582D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr"/>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N74" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -9232,7 +9224,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9246,7 +9238,7 @@
       <c r="U74" s="2" t="inlineStr"/>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
@@ -9256,17 +9248,17 @@
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
@@ -9276,13 +9268,17 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC74" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -9295,24 +9291,24 @@
       <c r="B75" s="2" t="inlineStr"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>07:10</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -9325,12 +9321,12 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>113分钟</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr"/>
@@ -9347,12 +9343,12 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9366,7 +9362,7 @@
       <c r="U75" s="2" t="inlineStr"/>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
@@ -9401,12 +9397,12 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>113.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AD75" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -9419,64 +9415,60 @@
       <c r="B76" s="2" t="inlineStr"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>沪A35683D</t>
+          <t>沪A51582D</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr"/>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N76" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr"/>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9490,7 +9482,7 @@
       <c r="U76" s="2" t="inlineStr"/>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
@@ -9500,17 +9492,17 @@
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
@@ -9520,17 +9512,13 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC76" s="2" t="inlineStr">
-        <is>
-          <t>91.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr"/>
       <c r="AD76" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -9543,7 +9531,7 @@
       <c r="B77" s="2" t="inlineStr"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -9553,7 +9541,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -9563,40 +9551,44 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>113分钟</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr"/>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N77" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9610,7 +9602,7 @@
       <c r="U77" s="2" t="inlineStr"/>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
@@ -9620,17 +9612,17 @@
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -9640,13 +9632,17 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC77" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>113.0</t>
+        </is>
+      </c>
       <c r="AD77" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -9659,24 +9655,24 @@
       <c r="B78" s="2" t="inlineStr"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A35683D</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -9689,12 +9685,12 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>106分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr"/>
@@ -9711,12 +9707,12 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9730,7 +9726,7 @@
       <c r="U78" s="2" t="inlineStr"/>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
@@ -9765,12 +9761,12 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AD78" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -9783,64 +9779,60 @@
       <c r="B79" s="2" t="inlineStr"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>97分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr"/>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N79" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr"/>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -9854,7 +9846,7 @@
       <c r="U79" s="2" t="inlineStr"/>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W79" s="2" t="inlineStr">
@@ -9864,17 +9856,17 @@
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
@@ -9884,17 +9876,13 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC79" s="2" t="inlineStr">
-        <is>
-          <t>97.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr"/>
       <c r="AD79" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -9907,7 +9895,7 @@
       <c r="B80" s="2" t="inlineStr"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>沪A53062D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -9917,7 +9905,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -9942,7 +9930,7 @@
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>94分钟</t>
+          <t>106分钟</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr"/>
@@ -9959,12 +9947,12 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -9978,7 +9966,7 @@
       <c r="U80" s="2" t="inlineStr"/>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
@@ -10003,22 +9991,22 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB80" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="AD80" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -10031,7 +10019,7 @@
       <c r="B81" s="2" t="inlineStr"/>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>沪A50235D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -10041,7 +10029,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>07:47</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -10061,7 +10049,7 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -10083,12 +10071,12 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -10102,7 +10090,7 @@
       <c r="U81" s="2" t="inlineStr"/>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>07:47</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W81" s="2" t="inlineStr">
@@ -10155,7 +10143,7 @@
       <c r="B82" s="2" t="inlineStr"/>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A53062D</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -10165,7 +10153,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -10175,40 +10163,44 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr"/>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N82" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -10222,7 +10214,7 @@
       <c r="U82" s="2" t="inlineStr"/>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W82" s="2" t="inlineStr">
@@ -10232,17 +10224,17 @@
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA82" s="2" t="inlineStr">
@@ -10252,13 +10244,17 @@
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC82" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
       <c r="AD82" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -10271,7 +10267,7 @@
       <c r="B83" s="2" t="inlineStr"/>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A50235D</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -10281,7 +10277,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>07:47</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -10291,32 +10287,36 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr"/>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N83" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -10338,7 +10338,7 @@
       <c r="U83" s="2" t="inlineStr"/>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>07:47</t>
         </is>
       </c>
       <c r="W83" s="2" t="inlineStr">
@@ -10348,17 +10348,17 @@
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA83" s="2" t="inlineStr">
@@ -10368,13 +10368,17 @@
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC83" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
       <c r="AD83" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -10387,7 +10391,7 @@
       <c r="B84" s="2" t="inlineStr"/>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>沪A53893D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -10397,7 +10401,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -10435,12 +10439,12 @@
       <c r="N84" s="2" t="inlineStr"/>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -10454,7 +10458,7 @@
       <c r="U84" s="2" t="inlineStr"/>
       <c r="V84" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W84" s="2" t="inlineStr">
@@ -10479,7 +10483,7 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
@@ -10503,22 +10507,22 @@
       <c r="B85" s="2" t="inlineStr"/>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -10551,12 +10555,12 @@
       <c r="N85" s="2" t="inlineStr"/>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -10570,7 +10574,7 @@
       <c r="U85" s="2" t="inlineStr"/>
       <c r="V85" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="W85" s="2" t="inlineStr">
@@ -10600,17 +10604,13 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC85" s="2" t="inlineStr">
-        <is>
-          <t>91.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr"/>
       <c r="AD85" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -10623,22 +10623,22 @@
       <c r="B86" s="2" t="inlineStr"/>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A53893D</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E86" s="2" t="inlineStr">
-        <is>
-          <t>08:20</t>
-        </is>
-      </c>
-      <c r="F86" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -10671,12 +10671,12 @@
       <c r="N86" s="2" t="inlineStr"/>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -10690,7 +10690,7 @@
       <c r="U86" s="2" t="inlineStr"/>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W86" s="2" t="inlineStr">
@@ -10715,7 +10715,7 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
@@ -10739,22 +10739,22 @@
       <c r="B87" s="2" t="inlineStr"/>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>沪A36930D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="inlineStr">
-        <is>
-          <t>08:25</t>
-        </is>
-      </c>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -10787,7 +10787,7 @@
       <c r="N87" s="2" t="inlineStr"/>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10806,7 +10806,7 @@
       <c r="U87" s="2" t="inlineStr"/>
       <c r="V87" s="2" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W87" s="2" t="inlineStr">
@@ -10831,18 +10831,22 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB87" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC87" s="2" t="inlineStr"/>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AD87" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -10855,22 +10859,22 @@
       <c r="B88" s="2" t="inlineStr"/>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E88" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F88" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -10903,12 +10907,12 @@
       <c r="N88" s="2" t="inlineStr"/>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -10922,7 +10926,7 @@
       <c r="U88" s="2" t="inlineStr"/>
       <c r="V88" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="W88" s="2" t="inlineStr">
@@ -10947,22 +10951,18 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC88" s="2" t="inlineStr">
-        <is>
-          <t>92.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr"/>
       <c r="AD88" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -10975,7 +10975,7 @@
       <c r="B89" s="2" t="inlineStr"/>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>沪A30829D</t>
+          <t>沪A36930D</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -10985,7 +10985,7 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
@@ -11023,12 +11023,12 @@
       <c r="N89" s="2" t="inlineStr"/>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -11042,7 +11042,7 @@
       <c r="U89" s="2" t="inlineStr"/>
       <c r="V89" s="2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="W89" s="2" t="inlineStr">
@@ -11067,7 +11067,7 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
@@ -11091,22 +11091,22 @@
       <c r="B90" s="2" t="inlineStr"/>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>沪A30260D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F90" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -11139,12 +11139,12 @@
       <c r="N90" s="2" t="inlineStr"/>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -11158,7 +11158,7 @@
       <c r="U90" s="2" t="inlineStr"/>
       <c r="V90" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W90" s="2" t="inlineStr">
@@ -11188,13 +11188,17 @@
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC90" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AD90" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -11207,22 +11211,22 @@
       <c r="B91" s="2" t="inlineStr"/>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A30829D</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -11255,12 +11259,12 @@
       <c r="N91" s="2" t="inlineStr"/>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -11274,7 +11278,7 @@
       <c r="U91" s="2" t="inlineStr"/>
       <c r="V91" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="W91" s="2" t="inlineStr">
@@ -11304,17 +11308,13 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC91" s="2" t="inlineStr">
-        <is>
-          <t>93.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr"/>
       <c r="AD91" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -11327,7 +11327,7 @@
       <c r="B92" s="2" t="inlineStr"/>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>沪A51582D</t>
+          <t>沪A30260D</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -11337,7 +11337,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -11375,12 +11375,12 @@
       <c r="N92" s="2" t="inlineStr"/>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -11394,7 +11394,7 @@
       <c r="U92" s="2" t="inlineStr"/>
       <c r="V92" s="2" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W92" s="2" t="inlineStr">
@@ -11443,7 +11443,7 @@
       <c r="B93" s="2" t="inlineStr"/>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>沪A35683D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -11453,7 +11453,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -11491,12 +11491,12 @@
       <c r="N93" s="2" t="inlineStr"/>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -11510,7 +11510,7 @@
       <c r="U93" s="2" t="inlineStr"/>
       <c r="V93" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W93" s="2" t="inlineStr">
@@ -11545,12 +11545,12 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AD93" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -11563,7 +11563,7 @@
       <c r="B94" s="2" t="inlineStr"/>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A51582D</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -11573,7 +11573,7 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -11611,12 +11611,12 @@
       <c r="N94" s="2" t="inlineStr"/>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -11630,7 +11630,7 @@
       <c r="U94" s="2" t="inlineStr"/>
       <c r="V94" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="W94" s="2" t="inlineStr">
@@ -11660,17 +11660,13 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC94" s="2" t="inlineStr">
-        <is>
-          <t>113.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr"/>
       <c r="AD94" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -11683,7 +11679,7 @@
       <c r="B95" s="2" t="inlineStr"/>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A35683D</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -11693,7 +11689,7 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -11731,12 +11727,12 @@
       <c r="N95" s="2" t="inlineStr"/>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -11750,7 +11746,7 @@
       <c r="U95" s="2" t="inlineStr"/>
       <c r="V95" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W95" s="2" t="inlineStr">
@@ -11785,12 +11781,12 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AD95" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -11803,7 +11799,7 @@
       <c r="B96" s="2" t="inlineStr"/>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -11813,7 +11809,7 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -11851,12 +11847,12 @@
       <c r="N96" s="2" t="inlineStr"/>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -11870,7 +11866,7 @@
       <c r="U96" s="2" t="inlineStr"/>
       <c r="V96" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W96" s="2" t="inlineStr">
@@ -11900,13 +11896,17 @@
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC96" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>113.0</t>
+        </is>
+      </c>
       <c r="AD96" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -11919,22 +11919,22 @@
       <c r="B97" s="2" t="inlineStr"/>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="F97" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       <c r="N97" s="2" t="inlineStr"/>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -11986,7 +11986,7 @@
       <c r="U97" s="2" t="inlineStr"/>
       <c r="V97" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="W97" s="2" t="inlineStr">
@@ -12021,12 +12021,12 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AD97" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -12039,22 +12039,22 @@
       <c r="B98" s="2" t="inlineStr"/>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>沪A50235D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E98" s="2" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
-      <c r="F98" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -12087,12 +12087,12 @@
       <c r="N98" s="2" t="inlineStr"/>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -12106,7 +12106,7 @@
       <c r="U98" s="2" t="inlineStr"/>
       <c r="V98" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="W98" s="2" t="inlineStr">
@@ -12136,17 +12136,13 @@
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC98" s="2" t="inlineStr">
-        <is>
-          <t>97.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr"/>
       <c r="AD98" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -12159,22 +12155,22 @@
       <c r="B99" s="2" t="inlineStr"/>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -12207,12 +12203,12 @@
       <c r="N99" s="2" t="inlineStr"/>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
@@ -12226,41 +12222,397 @@
       <c r="U99" s="2" t="inlineStr"/>
       <c r="V99" s="2" t="inlineStr">
         <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>106.0</t>
+        </is>
+      </c>
+      <c r="AD99" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr"/>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr"/>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr"/>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr"/>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="AD100" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr"/>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr"/>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr"/>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr"/>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr"/>
+      <c r="AD101" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr"/>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="W99" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr"/>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr"/>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr"/>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X99" s="2" t="inlineStr">
+      <c r="X102" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y99" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Z99" s="2" t="inlineStr">
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA99" s="2" t="inlineStr">
+      <c r="AA102" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB99" s="2" t="inlineStr">
+      <c r="AB102" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AC99" s="2" t="inlineStr"/>
-      <c r="AD99" s="2" t="inlineStr">
+      <c r="AC102" s="2" t="inlineStr"/>
+      <c r="AD102" s="2" t="inlineStr">
         <is>
           <t>—/18</t>
         </is>

--- a/data/export/2026-10-28-operations.xlsx
+++ b/data/export/2026-10-28-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD102"/>
+  <dimension ref="A1:AD126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2899,7 +2899,7 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
@@ -3340,7 +3340,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3499,7 +3499,7 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3851,7 +3851,7 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -4044,7 +4044,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4111,22 +4111,22 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A67026D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -4164,7 +4164,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4178,7 +4178,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4213,82 +4213,78 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4302,7 +4298,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4312,22 +4308,22 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
@@ -4337,40 +4333,40 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A02126A</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4403,12 +4399,12 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4422,7 +4418,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4458,77 +4454,73 @@
       <c r="AC33" s="2" t="inlineStr"/>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4542,7 +4534,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4552,22 +4544,22 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
@@ -4577,40 +4569,40 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4643,12 +4635,12 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:12</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4662,7 +4654,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4687,56 +4679,60 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC35" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A72305D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>疑似区间车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程38%处后消失；随后反向物理轨迹由seq28推进至seq60，推进32站，达到≥2站确认条件</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -4759,12 +4755,12 @@
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4772,21 +4768,13 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>白桦路明月路</t>
-        </is>
-      </c>
+      <c r="R36" s="2" t="inlineStr"/>
       <c r="S36" s="2" t="inlineStr"/>
       <c r="T36" s="2" t="inlineStr"/>
-      <c r="U36" s="2" t="inlineStr">
-        <is>
-          <t>区间折返已由主分类器确认；折返点按重建物理位置seq25映射；现有采样不足以把折返发车时间控制在±10分钟</t>
-        </is>
-      </c>
+      <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4811,88 +4799,88 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC36" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>154分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4906,7 +4894,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4916,22 +4904,22 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
@@ -4941,40 +4929,40 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -5007,12 +4995,12 @@
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5026,7 +5014,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5051,7 +5039,7 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
@@ -5062,35 +5050,35 @@
       <c r="AC38" s="2" t="inlineStr"/>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -5123,12 +5111,12 @@
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5142,7 +5130,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5167,7 +5155,7 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
@@ -5178,7 +5166,7 @@
       <c r="AC39" s="2" t="inlineStr"/>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -5191,55 +5179,59 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5258,7 +5250,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5268,17 +5260,17 @@
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5288,13 +5280,17 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC40" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -5307,7 +5303,7 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -5317,7 +5313,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -5355,12 +5351,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5374,7 +5370,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5399,7 +5395,7 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
@@ -5423,7 +5419,7 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -5433,7 +5429,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -5443,35 +5439,39 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr"/>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5490,7 +5490,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5500,17 +5500,17 @@
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5520,13 +5520,17 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC42" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -5539,22 +5543,22 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5587,12 +5591,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5606,7 +5610,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5631,7 +5635,7 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
@@ -5655,32 +5659,32 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程38%处后消失；随后反向物理轨迹由seq28推进至seq60，推进32站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -5703,7 +5707,7 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5716,13 +5720,21 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>白桦路明月路</t>
+        </is>
+      </c>
       <c r="S44" s="2" t="inlineStr"/>
       <c r="T44" s="2" t="inlineStr"/>
-      <c r="U44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq25映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5747,7 +5759,7 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
@@ -5771,55 +5783,59 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>07:24</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>疑似区间车</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程19%处后消失；随后反向物理轨迹由seq37推进至seq45，推进8站，达到≥2站确认条件</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>154分钟</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr"/>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5832,25 +5848,13 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R45" s="2" t="inlineStr">
-        <is>
-          <t>川周公路康沈路</t>
-        </is>
-      </c>
-      <c r="S45" s="2" t="inlineStr">
-        <is>
-          <t>07:41</t>
-        </is>
-      </c>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
       <c r="T45" s="2" t="inlineStr"/>
-      <c r="U45" s="2" t="inlineStr">
-        <is>
-          <t>区间折返已由主分类器确认；折返点按重建物理位置seq13映射；现有采样不足以把折返发车时间控制在±10分钟</t>
-        </is>
-      </c>
+      <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5860,33 +5864,37 @@
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB45" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC45" s="2" t="inlineStr"/>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>154.0</t>
+        </is>
+      </c>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -5899,22 +5907,22 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5947,12 +5955,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5966,7 +5974,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5991,7 +5999,7 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
@@ -6015,22 +6023,22 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -6063,12 +6071,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6082,7 +6090,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6107,7 +6115,7 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
@@ -6131,22 +6139,22 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -6179,12 +6187,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6198,7 +6206,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6223,7 +6231,7 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
@@ -6247,7 +6255,7 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -6257,7 +6265,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -6295,12 +6303,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6314,7 +6322,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6339,7 +6347,7 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
@@ -6363,22 +6371,22 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -6411,12 +6419,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6430,7 +6438,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6455,7 +6463,7 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
@@ -6479,7 +6487,7 @@
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -6489,7 +6497,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -6527,12 +6535,12 @@
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6546,7 +6554,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6571,7 +6579,7 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
@@ -6595,22 +6603,22 @@
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6643,12 +6651,12 @@
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6662,7 +6670,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6687,7 +6695,7 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
@@ -6711,7 +6719,7 @@
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -6721,7 +6729,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -6731,12 +6739,12 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程19%处后消失；随后反向物理轨迹由seq37推进至seq45，推进8站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
@@ -6759,12 +6767,12 @@
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6772,13 +6780,25 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R53" s="2" t="inlineStr"/>
-      <c r="S53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr">
+        <is>
+          <t>川周公路康沈路</t>
+        </is>
+      </c>
+      <c r="S53" s="2" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
       <c r="T53" s="2" t="inlineStr"/>
-      <c r="U53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq13映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6827,22 +6847,22 @@
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6875,12 +6895,12 @@
       <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6894,7 +6914,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6919,7 +6939,7 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
@@ -6943,22 +6963,22 @@
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6991,12 +7011,12 @@
       <c r="N55" s="2" t="inlineStr"/>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7010,7 +7030,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -7035,7 +7055,7 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
@@ -7059,22 +7079,22 @@
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -7107,12 +7127,12 @@
       <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7126,7 +7146,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -7151,7 +7171,7 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
@@ -7175,22 +7195,22 @@
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -7223,12 +7243,12 @@
       <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7242,7 +7262,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7267,7 +7287,7 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
@@ -7291,7 +7311,7 @@
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -7301,7 +7321,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -7339,12 +7359,12 @@
       <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7358,7 +7378,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7383,7 +7403,7 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
@@ -7407,7 +7427,7 @@
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -7417,7 +7437,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -7455,12 +7475,12 @@
       <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7474,7 +7494,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7523,22 +7543,22 @@
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7571,7 +7591,7 @@
       <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7590,7 +7610,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7615,22 +7635,18 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC60" s="2" t="inlineStr">
-        <is>
-          <t>135.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr"/>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -7643,7 +7659,7 @@
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -7653,7 +7669,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -7696,7 +7712,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7710,7 +7726,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7735,22 +7751,18 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC61" s="2" t="inlineStr">
-        <is>
-          <t>140.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr"/>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -7763,22 +7775,22 @@
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7811,7 +7823,7 @@
       <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7830,7 +7842,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -7855,7 +7867,7 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
@@ -7879,7 +7891,7 @@
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A72305D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -7889,7 +7901,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -7946,7 +7958,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -7971,7 +7983,7 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
@@ -7995,7 +8007,7 @@
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -8005,7 +8017,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -8043,7 +8055,7 @@
       <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8062,7 +8074,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -8087,22 +8099,18 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC64" s="2" t="inlineStr">
-        <is>
-          <t>154.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr"/>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -8115,7 +8123,7 @@
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -8125,7 +8133,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -8182,7 +8190,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8207,7 +8215,7 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
@@ -8231,7 +8239,7 @@
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -8241,7 +8249,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -8279,12 +8287,12 @@
       <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8298,7 +8306,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8323,7 +8331,7 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
@@ -8347,7 +8355,7 @@
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -8357,7 +8365,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -8395,7 +8403,7 @@
       <c r="N67" s="2" t="inlineStr"/>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8414,7 +8422,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8463,7 +8471,7 @@
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -8473,7 +8481,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -8511,7 +8519,7 @@
       <c r="N68" s="2" t="inlineStr"/>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8530,7 +8538,7 @@
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
@@ -8560,41 +8568,45 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC68" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -8646,7 +8658,7 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
@@ -8676,41 +8688,45 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC69" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -8762,7 +8778,7 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -8787,7 +8803,7 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
@@ -8798,35 +8814,35 @@
       <c r="AC70" s="2" t="inlineStr"/>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>沪A30829D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -8878,7 +8894,7 @@
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
@@ -8914,77 +8930,73 @@
       <c r="AC71" s="2" t="inlineStr"/>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr"/>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N72" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr"/>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -8998,7 +9010,7 @@
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
@@ -9008,17 +9020,17 @@
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
@@ -9033,40 +9045,40 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>沪A30260D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -9099,7 +9111,7 @@
       <c r="N73" s="2" t="inlineStr"/>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9118,7 +9130,7 @@
       <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
@@ -9154,69 +9166,65 @@
       <c r="AC73" s="2" t="inlineStr"/>
       <c r="AD73" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr"/>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N74" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr"/>
       <c r="O74" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -9224,7 +9232,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9238,7 +9246,7 @@
       <c r="U74" s="2" t="inlineStr"/>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
@@ -9248,17 +9256,17 @@
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
@@ -9268,87 +9276,79 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC74" s="2" t="inlineStr">
-        <is>
-          <t>92.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr"/>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>93分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr"/>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N75" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr"/>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9362,7 +9362,7 @@
       <c r="U75" s="2" t="inlineStr"/>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
@@ -9372,17 +9372,17 @@
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
@@ -9392,45 +9392,41 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC75" s="2" t="inlineStr">
-        <is>
-          <t>93.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr"/>
       <c r="AD75" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>沪A51582D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -9463,12 +9459,12 @@
       <c r="N76" s="2" t="inlineStr"/>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9482,7 +9478,7 @@
       <c r="U76" s="2" t="inlineStr"/>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
@@ -9518,69 +9514,65 @@
       <c r="AC76" s="2" t="inlineStr"/>
       <c r="AD76" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>113分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr"/>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N77" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr"/>
       <c r="O77" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -9588,7 +9580,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9602,7 +9594,7 @@
       <c r="U77" s="2" t="inlineStr"/>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
@@ -9612,17 +9604,17 @@
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -9632,87 +9624,79 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC77" s="2" t="inlineStr">
-        <is>
-          <t>113.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr"/>
       <c r="AD77" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>沪A35683D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr"/>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N78" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr"/>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9726,7 +9710,7 @@
       <c r="U78" s="2" t="inlineStr"/>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
@@ -9736,17 +9720,17 @@
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
@@ -9756,45 +9740,41 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC78" s="2" t="inlineStr">
-        <is>
-          <t>91.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr"/>
       <c r="AD78" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -9827,12 +9807,12 @@
       <c r="N79" s="2" t="inlineStr"/>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -9846,7 +9826,7 @@
       <c r="U79" s="2" t="inlineStr"/>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="W79" s="2" t="inlineStr">
@@ -9882,77 +9862,73 @@
       <c r="AC79" s="2" t="inlineStr"/>
       <c r="AD79" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>106分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr"/>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N80" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr"/>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -9966,7 +9942,7 @@
       <c r="U80" s="2" t="inlineStr"/>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
@@ -9976,17 +9952,17 @@
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
@@ -9996,87 +9972,79 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC80" s="2" t="inlineStr">
-        <is>
-          <t>106.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr"/>
       <c r="AD80" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr"/>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>97分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr"/>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N81" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr"/>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -10090,7 +10058,7 @@
       <c r="U81" s="2" t="inlineStr"/>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="W81" s="2" t="inlineStr">
@@ -10100,17 +10068,17 @@
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA81" s="2" t="inlineStr">
@@ -10120,79 +10088,71 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC81" s="2" t="inlineStr">
-        <is>
-          <t>97.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr"/>
       <c r="AD81" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr"/>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>沪A53062D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>94分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr"/>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N82" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr"/>
       <c r="O82" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -10200,7 +10160,7 @@
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -10214,7 +10174,7 @@
       <c r="U82" s="2" t="inlineStr"/>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="W82" s="2" t="inlineStr">
@@ -10224,107 +10184,99 @@
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC82" s="2" t="inlineStr">
-        <is>
-          <t>94.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr"/>
       <c r="AD82" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr"/>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>沪A50235D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>07:47</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>97分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr"/>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N83" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr"/>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -10338,7 +10290,7 @@
       <c r="U83" s="2" t="inlineStr"/>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>07:47</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="W83" s="2" t="inlineStr">
@@ -10348,17 +10300,17 @@
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA83" s="2" t="inlineStr">
@@ -10368,45 +10320,41 @@
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC83" s="2" t="inlineStr">
-        <is>
-          <t>97.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr"/>
       <c r="AD83" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr"/>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -10439,12 +10387,12 @@
       <c r="N84" s="2" t="inlineStr"/>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -10458,7 +10406,7 @@
       <c r="U84" s="2" t="inlineStr"/>
       <c r="V84" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="W84" s="2" t="inlineStr">
@@ -10494,35 +10442,35 @@
       <c r="AC84" s="2" t="inlineStr"/>
       <c r="AD84" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr"/>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -10555,12 +10503,12 @@
       <c r="N85" s="2" t="inlineStr"/>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -10574,7 +10522,7 @@
       <c r="U85" s="2" t="inlineStr"/>
       <c r="V85" s="2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="W85" s="2" t="inlineStr">
@@ -10610,7 +10558,7 @@
       <c r="AC85" s="2" t="inlineStr"/>
       <c r="AD85" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -10623,7 +10571,7 @@
       <c r="B86" s="2" t="inlineStr"/>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>沪A53893D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -10633,7 +10581,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -10671,7 +10619,7 @@
       <c r="N86" s="2" t="inlineStr"/>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10690,7 +10638,7 @@
       <c r="U86" s="2" t="inlineStr"/>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W86" s="2" t="inlineStr">
@@ -10715,7 +10663,7 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
@@ -10739,7 +10687,7 @@
       <c r="B87" s="2" t="inlineStr"/>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -10749,7 +10697,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -10787,12 +10735,12 @@
       <c r="N87" s="2" t="inlineStr"/>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
@@ -10806,7 +10754,7 @@
       <c r="U87" s="2" t="inlineStr"/>
       <c r="V87" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="W87" s="2" t="inlineStr">
@@ -10831,22 +10779,18 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC87" s="2" t="inlineStr">
-        <is>
-          <t>91.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr"/>
       <c r="AD87" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -10859,22 +10803,22 @@
       <c r="B88" s="2" t="inlineStr"/>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A30829D</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E88" s="2" t="inlineStr">
-        <is>
-          <t>08:20</t>
-        </is>
-      </c>
-      <c r="F88" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -10912,7 +10856,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -10926,7 +10870,7 @@
       <c r="U88" s="2" t="inlineStr"/>
       <c r="V88" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W88" s="2" t="inlineStr">
@@ -10975,7 +10919,7 @@
       <c r="B89" s="2" t="inlineStr"/>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>沪A36930D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -10985,7 +10929,7 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
@@ -10995,40 +10939,44 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr"/>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N89" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -11042,7 +10990,7 @@
       <c r="U89" s="2" t="inlineStr"/>
       <c r="V89" s="2" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W89" s="2" t="inlineStr">
@@ -11052,33 +11000,37 @@
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB89" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC89" s="2" t="inlineStr"/>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AD89" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -11091,7 +11043,7 @@
       <c r="B90" s="2" t="inlineStr"/>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A30260D</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -11101,7 +11053,7 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
@@ -11139,12 +11091,12 @@
       <c r="N90" s="2" t="inlineStr"/>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -11158,7 +11110,7 @@
       <c r="U90" s="2" t="inlineStr"/>
       <c r="V90" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W90" s="2" t="inlineStr">
@@ -11188,17 +11140,13 @@
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC90" s="2" t="inlineStr">
-        <is>
-          <t>92.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr"/>
       <c r="AD90" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -11211,7 +11159,7 @@
       <c r="B91" s="2" t="inlineStr"/>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>沪A30829D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -11221,7 +11169,7 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
@@ -11231,40 +11179,44 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr"/>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N91" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -11278,7 +11230,7 @@
       <c r="U91" s="2" t="inlineStr"/>
       <c r="V91" s="2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W91" s="2" t="inlineStr">
@@ -11288,33 +11240,37 @@
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC91" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AD91" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -11327,7 +11283,7 @@
       <c r="B92" s="2" t="inlineStr"/>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>沪A30260D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -11337,7 +11293,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -11347,40 +11303,44 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr"/>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N92" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -11394,7 +11354,7 @@
       <c r="U92" s="2" t="inlineStr"/>
       <c r="V92" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W92" s="2" t="inlineStr">
@@ -11404,33 +11364,37 @@
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC92" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
       <c r="AD92" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -11443,7 +11407,7 @@
       <c r="B93" s="2" t="inlineStr"/>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A51582D</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -11453,7 +11417,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -11496,7 +11460,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -11510,7 +11474,7 @@
       <c r="U93" s="2" t="inlineStr"/>
       <c r="V93" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W93" s="2" t="inlineStr">
@@ -11535,22 +11499,18 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC93" s="2" t="inlineStr">
-        <is>
-          <t>93.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr"/>
       <c r="AD93" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -11563,55 +11523,59 @@
       <c r="B94" s="2" t="inlineStr"/>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>沪A51582D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
-        <is>
-          <t>08:57</t>
-        </is>
-      </c>
-      <c r="F94" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>113分钟</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr"/>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N94" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11630,7 +11594,7 @@
       <c r="U94" s="2" t="inlineStr"/>
       <c r="V94" s="2" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W94" s="2" t="inlineStr">
@@ -11640,17 +11604,17 @@
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA94" s="2" t="inlineStr">
@@ -11660,13 +11624,17 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC94" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>113.0</t>
+        </is>
+      </c>
       <c r="AD94" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -11684,47 +11652,51 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F95" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr"/>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N95" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -11732,7 +11704,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -11746,7 +11718,7 @@
       <c r="U95" s="2" t="inlineStr"/>
       <c r="V95" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W95" s="2" t="inlineStr">
@@ -11756,22 +11728,22 @@
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
@@ -11799,22 +11771,22 @@
       <c r="B96" s="2" t="inlineStr"/>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E96" s="2" t="inlineStr">
-        <is>
-          <t>09:10</t>
-        </is>
-      </c>
-      <c r="F96" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -11847,12 +11819,12 @@
       <c r="N96" s="2" t="inlineStr"/>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -11866,7 +11838,7 @@
       <c r="U96" s="2" t="inlineStr"/>
       <c r="V96" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W96" s="2" t="inlineStr">
@@ -11891,22 +11863,18 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC96" s="2" t="inlineStr">
-        <is>
-          <t>113.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr"/>
       <c r="AD96" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -11919,7 +11887,7 @@
       <c r="B97" s="2" t="inlineStr"/>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -11929,7 +11897,7 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
@@ -11939,35 +11907,39 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>106分钟</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr"/>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N97" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11986,7 +11958,7 @@
       <c r="U97" s="2" t="inlineStr"/>
       <c r="V97" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W97" s="2" t="inlineStr">
@@ -11996,17 +11968,17 @@
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA97" s="2" t="inlineStr">
@@ -12021,12 +11993,12 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="AD97" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -12039,7 +12011,7 @@
       <c r="B98" s="2" t="inlineStr"/>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -12049,7 +12021,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -12059,35 +12031,39 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr"/>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N98" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12106,7 +12082,7 @@
       <c r="U98" s="2" t="inlineStr"/>
       <c r="V98" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W98" s="2" t="inlineStr">
@@ -12116,17 +12092,17 @@
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z98" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA98" s="2" t="inlineStr">
@@ -12136,13 +12112,17 @@
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC98" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
       <c r="AD98" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -12155,60 +12135,64 @@
       <c r="B99" s="2" t="inlineStr"/>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A53062D</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr"/>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N99" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
@@ -12222,7 +12206,7 @@
       <c r="U99" s="2" t="inlineStr"/>
       <c r="V99" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W99" s="2" t="inlineStr">
@@ -12232,22 +12216,22 @@
       </c>
       <c r="X99" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z99" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA99" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB99" s="2" t="inlineStr">
@@ -12257,12 +12241,12 @@
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AD99" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -12280,47 +12264,51 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
-      <c r="F100" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr"/>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N100" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -12328,7 +12316,7 @@
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
@@ -12342,7 +12330,7 @@
       <c r="U100" s="2" t="inlineStr"/>
       <c r="V100" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>07:47</t>
         </is>
       </c>
       <c r="W100" s="2" t="inlineStr">
@@ -12352,17 +12340,17 @@
       </c>
       <c r="X100" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z100" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA100" s="2" t="inlineStr">
@@ -12400,17 +12388,17 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E101" s="2" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="F101" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -12448,7 +12436,7 @@
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
@@ -12462,7 +12450,7 @@
       <c r="U101" s="2" t="inlineStr"/>
       <c r="V101" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W101" s="2" t="inlineStr">
@@ -12511,22 +12499,22 @@
       <c r="B102" s="2" t="inlineStr"/>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="F102" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -12578,7 +12566,7 @@
       <c r="U102" s="2" t="inlineStr"/>
       <c r="V102" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="W102" s="2" t="inlineStr">
@@ -12603,7 +12591,7 @@
       </c>
       <c r="AA102" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB102" s="2" t="inlineStr">
@@ -12613,6 +12601,2838 @@
       </c>
       <c r="AC102" s="2" t="inlineStr"/>
       <c r="AD102" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr"/>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>沪A53893D</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr"/>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr"/>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr"/>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr"/>
+      <c r="AD103" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr"/>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr"/>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="inlineStr"/>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R104" s="2" t="inlineStr"/>
+      <c r="S104" s="2" t="inlineStr"/>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr"/>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z104" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA104" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AD104" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr"/>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr"/>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="inlineStr"/>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R105" s="2" t="inlineStr"/>
+      <c r="S105" s="2" t="inlineStr"/>
+      <c r="T105" s="2" t="inlineStr"/>
+      <c r="U105" s="2" t="inlineStr"/>
+      <c r="V105" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="W105" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X105" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z105" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA105" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB105" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC105" s="2" t="inlineStr"/>
+      <c r="AD105" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr"/>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr"/>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N106" s="2" t="inlineStr"/>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q106" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R106" s="2" t="inlineStr"/>
+      <c r="S106" s="2" t="inlineStr"/>
+      <c r="T106" s="2" t="inlineStr"/>
+      <c r="U106" s="2" t="inlineStr"/>
+      <c r="V106" s="2" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="W106" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X106" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z106" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA106" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB106" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC106" s="2" t="inlineStr"/>
+      <c r="AD106" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr"/>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr"/>
+      <c r="L107" s="2" t="inlineStr"/>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N107" s="2" t="inlineStr"/>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P107" s="2" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="Q107" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R107" s="2" t="inlineStr"/>
+      <c r="S107" s="2" t="inlineStr"/>
+      <c r="T107" s="2" t="inlineStr"/>
+      <c r="U107" s="2" t="inlineStr"/>
+      <c r="V107" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W107" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X107" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z107" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA107" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB107" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC107" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AD107" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr"/>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>沪A30829D</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr"/>
+      <c r="L108" s="2" t="inlineStr"/>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="inlineStr"/>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P108" s="2" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="Q108" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R108" s="2" t="inlineStr"/>
+      <c r="S108" s="2" t="inlineStr"/>
+      <c r="T108" s="2" t="inlineStr"/>
+      <c r="U108" s="2" t="inlineStr"/>
+      <c r="V108" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="W108" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X108" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z108" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA108" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB108" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC108" s="2" t="inlineStr"/>
+      <c r="AD108" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr"/>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>沪A30260D</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr"/>
+      <c r="L109" s="2" t="inlineStr"/>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N109" s="2" t="inlineStr"/>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P109" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q109" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R109" s="2" t="inlineStr"/>
+      <c r="S109" s="2" t="inlineStr"/>
+      <c r="T109" s="2" t="inlineStr"/>
+      <c r="U109" s="2" t="inlineStr"/>
+      <c r="V109" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W109" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X109" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y109" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z109" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA109" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB109" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC109" s="2" t="inlineStr"/>
+      <c r="AD109" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr"/>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr"/>
+      <c r="L110" s="2" t="inlineStr"/>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N110" s="2" t="inlineStr"/>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P110" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="Q110" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R110" s="2" t="inlineStr"/>
+      <c r="S110" s="2" t="inlineStr"/>
+      <c r="T110" s="2" t="inlineStr"/>
+      <c r="U110" s="2" t="inlineStr"/>
+      <c r="V110" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W110" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X110" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y110" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z110" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA110" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB110" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC110" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AD110" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr"/>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>沪A51582D</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr"/>
+      <c r="L111" s="2" t="inlineStr"/>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N111" s="2" t="inlineStr"/>
+      <c r="O111" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P111" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="Q111" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R111" s="2" t="inlineStr"/>
+      <c r="S111" s="2" t="inlineStr"/>
+      <c r="T111" s="2" t="inlineStr"/>
+      <c r="U111" s="2" t="inlineStr"/>
+      <c r="V111" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="W111" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X111" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y111" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z111" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA111" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB111" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC111" s="2" t="inlineStr"/>
+      <c r="AD111" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr"/>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>沪A35683D</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr"/>
+      <c r="L112" s="2" t="inlineStr"/>
+      <c r="M112" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N112" s="2" t="inlineStr"/>
+      <c r="O112" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P112" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="Q112" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R112" s="2" t="inlineStr"/>
+      <c r="S112" s="2" t="inlineStr"/>
+      <c r="T112" s="2" t="inlineStr"/>
+      <c r="U112" s="2" t="inlineStr"/>
+      <c r="V112" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W112" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X112" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y112" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z112" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA112" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB112" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC112" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AD112" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr"/>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr"/>
+      <c r="L113" s="2" t="inlineStr"/>
+      <c r="M113" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N113" s="2" t="inlineStr"/>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P113" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q113" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R113" s="2" t="inlineStr"/>
+      <c r="S113" s="2" t="inlineStr"/>
+      <c r="T113" s="2" t="inlineStr"/>
+      <c r="U113" s="2" t="inlineStr"/>
+      <c r="V113" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="W113" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X113" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y113" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z113" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA113" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB113" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC113" s="2" t="inlineStr">
+        <is>
+          <t>113.0</t>
+        </is>
+      </c>
+      <c r="AD113" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr"/>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr"/>
+      <c r="L114" s="2" t="inlineStr"/>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N114" s="2" t="inlineStr"/>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P114" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q114" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R114" s="2" t="inlineStr"/>
+      <c r="S114" s="2" t="inlineStr"/>
+      <c r="T114" s="2" t="inlineStr"/>
+      <c r="U114" s="2" t="inlineStr"/>
+      <c r="V114" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="W114" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X114" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y114" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z114" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA114" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB114" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC114" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="AD114" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr"/>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr"/>
+      <c r="L115" s="2" t="inlineStr"/>
+      <c r="M115" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N115" s="2" t="inlineStr"/>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P115" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="Q115" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R115" s="2" t="inlineStr"/>
+      <c r="S115" s="2" t="inlineStr"/>
+      <c r="T115" s="2" t="inlineStr"/>
+      <c r="U115" s="2" t="inlineStr"/>
+      <c r="V115" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="W115" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X115" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y115" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z115" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA115" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB115" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC115" s="2" t="inlineStr"/>
+      <c r="AD115" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr"/>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr"/>
+      <c r="L116" s="2" t="inlineStr"/>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N116" s="2" t="inlineStr"/>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P116" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q116" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R116" s="2" t="inlineStr"/>
+      <c r="S116" s="2" t="inlineStr"/>
+      <c r="T116" s="2" t="inlineStr"/>
+      <c r="U116" s="2" t="inlineStr"/>
+      <c r="V116" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W116" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X116" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y116" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z116" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA116" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB116" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC116" s="2" t="inlineStr">
+        <is>
+          <t>106.0</t>
+        </is>
+      </c>
+      <c r="AD116" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr"/>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr"/>
+      <c r="L117" s="2" t="inlineStr"/>
+      <c r="M117" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N117" s="2" t="inlineStr"/>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P117" s="2" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="Q117" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R117" s="2" t="inlineStr"/>
+      <c r="S117" s="2" t="inlineStr"/>
+      <c r="T117" s="2" t="inlineStr"/>
+      <c r="U117" s="2" t="inlineStr"/>
+      <c r="V117" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="W117" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X117" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y117" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z117" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA117" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB117" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC117" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="AD117" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr"/>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr"/>
+      <c r="L118" s="2" t="inlineStr"/>
+      <c r="M118" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N118" s="2" t="inlineStr"/>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P118" s="2" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="Q118" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R118" s="2" t="inlineStr"/>
+      <c r="S118" s="2" t="inlineStr"/>
+      <c r="T118" s="2" t="inlineStr"/>
+      <c r="U118" s="2" t="inlineStr"/>
+      <c r="V118" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="W118" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X118" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y118" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z118" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA118" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB118" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC118" s="2" t="inlineStr"/>
+      <c r="AD118" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr"/>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr"/>
+      <c r="L119" s="2" t="inlineStr"/>
+      <c r="M119" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N119" s="2" t="inlineStr"/>
+      <c r="O119" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P119" s="2" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="Q119" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R119" s="2" t="inlineStr"/>
+      <c r="S119" s="2" t="inlineStr"/>
+      <c r="T119" s="2" t="inlineStr"/>
+      <c r="U119" s="2" t="inlineStr"/>
+      <c r="V119" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="W119" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X119" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y119" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z119" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA119" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB119" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC119" s="2" t="inlineStr"/>
+      <c r="AD119" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr"/>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr"/>
+      <c r="L120" s="2" t="inlineStr"/>
+      <c r="M120" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N120" s="2" t="inlineStr"/>
+      <c r="O120" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P120" s="2" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="Q120" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R120" s="2" t="inlineStr"/>
+      <c r="S120" s="2" t="inlineStr"/>
+      <c r="T120" s="2" t="inlineStr"/>
+      <c r="U120" s="2" t="inlineStr"/>
+      <c r="V120" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="W120" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X120" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y120" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z120" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA120" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB120" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC120" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AD120" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr"/>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>沪A30829D</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr"/>
+      <c r="L121" s="2" t="inlineStr"/>
+      <c r="M121" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N121" s="2" t="inlineStr"/>
+      <c r="O121" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P121" s="2" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="Q121" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R121" s="2" t="inlineStr"/>
+      <c r="S121" s="2" t="inlineStr"/>
+      <c r="T121" s="2" t="inlineStr"/>
+      <c r="U121" s="2" t="inlineStr"/>
+      <c r="V121" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="W121" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X121" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y121" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z121" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA121" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB121" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC121" s="2" t="inlineStr"/>
+      <c r="AD121" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr"/>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr"/>
+      <c r="L122" s="2" t="inlineStr"/>
+      <c r="M122" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N122" s="2" t="inlineStr"/>
+      <c r="O122" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P122" s="2" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="Q122" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R122" s="2" t="inlineStr"/>
+      <c r="S122" s="2" t="inlineStr"/>
+      <c r="T122" s="2" t="inlineStr"/>
+      <c r="U122" s="2" t="inlineStr"/>
+      <c r="V122" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="W122" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X122" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y122" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z122" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA122" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB122" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC122" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AD122" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr"/>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr"/>
+      <c r="L123" s="2" t="inlineStr"/>
+      <c r="M123" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N123" s="2" t="inlineStr"/>
+      <c r="O123" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P123" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="Q123" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R123" s="2" t="inlineStr"/>
+      <c r="S123" s="2" t="inlineStr"/>
+      <c r="T123" s="2" t="inlineStr"/>
+      <c r="U123" s="2" t="inlineStr"/>
+      <c r="V123" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="W123" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X123" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y123" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z123" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA123" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB123" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC123" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AD123" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr"/>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>沪A35683D</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr"/>
+      <c r="L124" s="2" t="inlineStr"/>
+      <c r="M124" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N124" s="2" t="inlineStr"/>
+      <c r="O124" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P124" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="Q124" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R124" s="2" t="inlineStr"/>
+      <c r="S124" s="2" t="inlineStr"/>
+      <c r="T124" s="2" t="inlineStr"/>
+      <c r="U124" s="2" t="inlineStr"/>
+      <c r="V124" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="W124" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X124" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y124" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z124" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA124" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB124" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC124" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AD124" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr"/>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>沪A51582D</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr"/>
+      <c r="L125" s="2" t="inlineStr"/>
+      <c r="M125" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N125" s="2" t="inlineStr"/>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P125" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="Q125" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R125" s="2" t="inlineStr"/>
+      <c r="S125" s="2" t="inlineStr"/>
+      <c r="T125" s="2" t="inlineStr"/>
+      <c r="U125" s="2" t="inlineStr"/>
+      <c r="V125" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="W125" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X125" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y125" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z125" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA125" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB125" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC125" s="2" t="inlineStr"/>
+      <c r="AD125" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr"/>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr"/>
+      <c r="L126" s="2" t="inlineStr"/>
+      <c r="M126" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N126" s="2" t="inlineStr"/>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P126" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="Q126" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R126" s="2" t="inlineStr"/>
+      <c r="S126" s="2" t="inlineStr"/>
+      <c r="T126" s="2" t="inlineStr"/>
+      <c r="U126" s="2" t="inlineStr"/>
+      <c r="V126" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="W126" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X126" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y126" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z126" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA126" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB126" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC126" s="2" t="inlineStr"/>
+      <c r="AD126" s="2" t="inlineStr">
         <is>
           <t>—/18</t>
         </is>

--- a/data/export/2026-10-28-operations.xlsx
+++ b/data/export/2026-10-28-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD126"/>
+  <dimension ref="A1:AD144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2779,7 +2779,7 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3340,7 +3340,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3692,7 +3692,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
@@ -4044,7 +4044,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4083,7 +4083,7 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4323,7 +4323,7 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4640,7 +4640,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -5000,7 +5000,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5063,22 +5063,22 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A55712D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -5111,12 +5111,12 @@
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5130,7 +5130,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5155,88 +5155,88 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>92.5</t>
+        </is>
+      </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5250,7 +5250,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5260,65 +5260,61 @@
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC40" s="2" t="inlineStr">
-        <is>
-          <t>135.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr"/>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -5351,12 +5347,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5370,7 +5366,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5395,88 +5391,88 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC41" s="2" t="inlineStr"/>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>84.5</t>
+        </is>
+      </c>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A12050A</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr"/>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5490,7 +5486,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5500,65 +5496,61 @@
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC42" s="2" t="inlineStr">
-        <is>
-          <t>140.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr"/>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5591,12 +5583,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5610,7 +5602,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5635,56 +5627,60 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC43" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A72305D</t>
+          <t>沪A02126A</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>疑似区间车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程38%处后消失；随后反向物理轨迹由seq28推进至seq60，推进32站，达到≥2站确认条件</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -5707,12 +5703,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5720,21 +5716,13 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R44" s="2" t="inlineStr">
-        <is>
-          <t>白桦路明月路</t>
-        </is>
-      </c>
+      <c r="R44" s="2" t="inlineStr"/>
       <c r="S44" s="2" t="inlineStr"/>
       <c r="T44" s="2" t="inlineStr"/>
-      <c r="U44" s="2" t="inlineStr">
-        <is>
-          <t>区间折返已由主分类器确认；折返点按重建物理位置seq25映射；现有采样不足以把折返发车时间控制在±10分钟</t>
-        </is>
-      </c>
+      <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5759,7 +5747,7 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
@@ -5770,7 +5758,7 @@
       <c r="AC44" s="2" t="inlineStr"/>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -5783,7 +5771,7 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -5793,7 +5781,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -5813,12 +5801,12 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>154分钟</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr"/>
@@ -5835,7 +5823,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5854,7 +5842,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5889,12 +5877,12 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -5907,7 +5895,7 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -5917,7 +5905,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -5974,7 +5962,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -6023,7 +6011,7 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -6033,7 +6021,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -6043,40 +6031,44 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr"/>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N47" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6090,7 +6082,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6100,33 +6092,37 @@
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC47" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6135,7 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -6149,7 +6145,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -6187,12 +6183,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6206,7 +6202,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6231,7 +6227,7 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
@@ -6255,32 +6251,32 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程38%处后消失；随后反向物理轨迹由seq28推进至seq60，推进32站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
@@ -6303,12 +6299,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6316,13 +6312,21 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr">
+        <is>
+          <t>白桦路明月路</t>
+        </is>
+      </c>
       <c r="S49" s="2" t="inlineStr"/>
       <c r="T49" s="2" t="inlineStr"/>
-      <c r="U49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq25映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6371,7 +6375,7 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -6381,7 +6385,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -6391,40 +6395,44 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>154分钟</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr"/>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N50" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6438,7 +6446,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6448,17 +6456,17 @@
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6468,13 +6476,17 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC50" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>154.0</t>
+        </is>
+      </c>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -6487,22 +6499,22 @@
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6535,12 +6547,12 @@
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6554,7 +6566,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6603,22 +6615,22 @@
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6651,12 +6663,12 @@
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6670,7 +6682,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6719,7 +6731,7 @@
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -6729,7 +6741,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -6739,12 +6751,12 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>疑似区间车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程19%处后消失；随后反向物理轨迹由seq37推进至seq45，推进8站，达到≥2站确认条件</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
@@ -6767,12 +6779,12 @@
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6780,25 +6792,13 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R53" s="2" t="inlineStr">
-        <is>
-          <t>川周公路康沈路</t>
-        </is>
-      </c>
-      <c r="S53" s="2" t="inlineStr">
-        <is>
-          <t>07:41</t>
-        </is>
-      </c>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
       <c r="T53" s="2" t="inlineStr"/>
-      <c r="U53" s="2" t="inlineStr">
-        <is>
-          <t>区间折返已由主分类器确认；折返点按重建物理位置seq13映射；现有采样不足以把折返发车时间控制在±10分钟</t>
-        </is>
-      </c>
+      <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6823,7 +6823,7 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
@@ -6847,22 +6847,22 @@
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6895,12 +6895,12 @@
       <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6914,7 +6914,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6963,22 +6963,22 @@
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -7011,12 +7011,12 @@
       <c r="N55" s="2" t="inlineStr"/>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7030,7 +7030,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -7079,7 +7079,7 @@
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -7127,12 +7127,12 @@
       <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7146,7 +7146,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -7195,7 +7195,7 @@
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -7205,7 +7205,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -7243,12 +7243,12 @@
       <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7262,7 +7262,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7311,7 +7311,7 @@
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -7331,12 +7331,12 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程19%处后消失；随后反向物理轨迹由seq37推进至seq45，推进8站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -7359,12 +7359,12 @@
       <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7372,13 +7372,25 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R58" s="2" t="inlineStr"/>
-      <c r="S58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr">
+        <is>
+          <t>川周公路康沈路</t>
+        </is>
+      </c>
+      <c r="S58" s="2" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
       <c r="T58" s="2" t="inlineStr"/>
-      <c r="U58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq13映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7403,7 +7415,7 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
@@ -7427,7 +7439,7 @@
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -7437,7 +7449,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -7475,7 +7487,7 @@
       <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7494,7 +7506,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7543,22 +7555,22 @@
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7591,12 +7603,12 @@
       <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7610,7 +7622,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7635,7 +7647,7 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
@@ -7659,22 +7671,22 @@
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7707,12 +7719,12 @@
       <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7726,7 +7738,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7751,7 +7763,7 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
@@ -7775,7 +7787,7 @@
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -7785,7 +7797,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -7823,12 +7835,12 @@
       <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7842,7 +7854,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -7867,7 +7879,7 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
@@ -7891,22 +7903,22 @@
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7939,12 +7951,12 @@
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7958,7 +7970,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -7983,7 +7995,7 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
@@ -8007,22 +8019,22 @@
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -8055,12 +8067,12 @@
       <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8074,7 +8086,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -8099,7 +8111,7 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
@@ -8123,7 +8135,7 @@
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -8133,7 +8145,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -8171,12 +8183,12 @@
       <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8190,7 +8202,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8215,7 +8227,7 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
@@ -8239,7 +8251,7 @@
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -8249,7 +8261,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -8287,12 +8299,12 @@
       <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8306,7 +8318,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8355,22 +8367,22 @@
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>08:55</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -8403,12 +8415,12 @@
       <c r="N67" s="2" t="inlineStr"/>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8422,7 +8434,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8471,22 +8483,22 @@
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -8538,7 +8550,7 @@
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
@@ -8563,22 +8575,18 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC68" s="2" t="inlineStr">
-        <is>
-          <t>135.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr"/>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -8591,7 +8599,7 @@
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -8601,7 +8609,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -8658,7 +8666,7 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
@@ -8683,22 +8691,18 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC69" s="2" t="inlineStr">
-        <is>
-          <t>140.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr"/>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -8711,7 +8715,7 @@
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -8721,7 +8725,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -8764,7 +8768,7 @@
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8778,7 +8782,7 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -8827,22 +8831,22 @@
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>沪A72305D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>09:24</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -8875,12 +8879,12 @@
       <c r="N71" s="2" t="inlineStr"/>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8894,7 +8898,7 @@
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
@@ -8943,22 +8947,22 @@
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -8991,7 +8995,7 @@
       <c r="N72" s="2" t="inlineStr"/>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9010,7 +9014,7 @@
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
@@ -9040,17 +9044,13 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC72" s="2" t="inlineStr">
-        <is>
-          <t>154.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr"/>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -9063,22 +9063,22 @@
       <c r="B73" s="2" t="inlineStr"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -9130,7 +9130,7 @@
       <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
@@ -9160,13 +9160,17 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC73" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
       <c r="AD73" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -9179,7 +9183,7 @@
       <c r="B74" s="2" t="inlineStr"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -9189,7 +9193,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -9227,12 +9231,12 @@
       <c r="N74" s="2" t="inlineStr"/>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9246,7 +9250,7 @@
       <c r="U74" s="2" t="inlineStr"/>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
@@ -9271,18 +9275,22 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC74" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -9295,7 +9303,7 @@
       <c r="B75" s="2" t="inlineStr"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -9305,7 +9313,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -9343,12 +9351,12 @@
       <c r="N75" s="2" t="inlineStr"/>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9362,7 +9370,7 @@
       <c r="U75" s="2" t="inlineStr"/>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
@@ -9387,7 +9395,7 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
@@ -9411,7 +9419,7 @@
       <c r="B76" s="2" t="inlineStr"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -9421,7 +9429,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -9459,12 +9467,12 @@
       <c r="N76" s="2" t="inlineStr"/>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9478,7 +9486,7 @@
       <c r="U76" s="2" t="inlineStr"/>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
@@ -9527,7 +9535,7 @@
       <c r="B77" s="2" t="inlineStr"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -9537,7 +9545,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -9575,12 +9583,12 @@
       <c r="N77" s="2" t="inlineStr"/>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9594,7 +9602,7 @@
       <c r="U77" s="2" t="inlineStr"/>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
@@ -9624,13 +9632,17 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC77" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>154.0</t>
+        </is>
+      </c>
       <c r="AD77" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -9643,22 +9655,22 @@
       <c r="B78" s="2" t="inlineStr"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -9691,12 +9703,12 @@
       <c r="N78" s="2" t="inlineStr"/>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9710,7 +9722,7 @@
       <c r="U78" s="2" t="inlineStr"/>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
@@ -9759,22 +9771,22 @@
       <c r="B79" s="2" t="inlineStr"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="inlineStr">
-        <is>
-          <t>10:19</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -9807,12 +9819,12 @@
       <c r="N79" s="2" t="inlineStr"/>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -9826,7 +9838,7 @@
       <c r="U79" s="2" t="inlineStr"/>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W79" s="2" t="inlineStr">
@@ -9875,7 +9887,7 @@
       <c r="B80" s="2" t="inlineStr"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -9885,7 +9897,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -9923,12 +9935,12 @@
       <c r="N80" s="2" t="inlineStr"/>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -9942,7 +9954,7 @@
       <c r="U80" s="2" t="inlineStr"/>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
@@ -9991,22 +10003,22 @@
       <c r="B81" s="2" t="inlineStr"/>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -10039,12 +10051,12 @@
       <c r="N81" s="2" t="inlineStr"/>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -10058,7 +10070,7 @@
       <c r="U81" s="2" t="inlineStr"/>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="W81" s="2" t="inlineStr">
@@ -10107,22 +10119,22 @@
       <c r="B82" s="2" t="inlineStr"/>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -10155,12 +10167,12 @@
       <c r="N82" s="2" t="inlineStr"/>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -10174,7 +10186,7 @@
       <c r="U82" s="2" t="inlineStr"/>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="W82" s="2" t="inlineStr">
@@ -10223,7 +10235,7 @@
       <c r="B83" s="2" t="inlineStr"/>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -10233,7 +10245,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -10271,12 +10283,12 @@
       <c r="N83" s="2" t="inlineStr"/>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -10290,7 +10302,7 @@
       <c r="U83" s="2" t="inlineStr"/>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="W83" s="2" t="inlineStr">
@@ -10339,7 +10351,7 @@
       <c r="B84" s="2" t="inlineStr"/>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -10349,7 +10361,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -10387,12 +10399,12 @@
       <c r="N84" s="2" t="inlineStr"/>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -10406,7 +10418,7 @@
       <c r="U84" s="2" t="inlineStr"/>
       <c r="V84" s="2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="W84" s="2" t="inlineStr">
@@ -10455,22 +10467,22 @@
       <c r="B85" s="2" t="inlineStr"/>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -10503,7 +10515,7 @@
       <c r="N85" s="2" t="inlineStr"/>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10522,7 +10534,7 @@
       <c r="U85" s="2" t="inlineStr"/>
       <c r="V85" s="2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="W85" s="2" t="inlineStr">
@@ -10565,28 +10577,28 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr"/>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -10619,12 +10631,12 @@
       <c r="N86" s="2" t="inlineStr"/>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -10638,7 +10650,7 @@
       <c r="U86" s="2" t="inlineStr"/>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="W86" s="2" t="inlineStr">
@@ -10674,35 +10686,35 @@
       <c r="AC86" s="2" t="inlineStr"/>
       <c r="AD86" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr"/>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -10735,12 +10747,12 @@
       <c r="N87" s="2" t="inlineStr"/>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
@@ -10754,7 +10766,7 @@
       <c r="U87" s="2" t="inlineStr"/>
       <c r="V87" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="W87" s="2" t="inlineStr">
@@ -10779,7 +10791,7 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
@@ -10790,35 +10802,35 @@
       <c r="AC87" s="2" t="inlineStr"/>
       <c r="AD87" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr"/>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>沪A30829D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -10851,12 +10863,12 @@
       <c r="N88" s="2" t="inlineStr"/>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -10870,7 +10882,7 @@
       <c r="U88" s="2" t="inlineStr"/>
       <c r="V88" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="W88" s="2" t="inlineStr">
@@ -10895,7 +10907,7 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
@@ -10906,77 +10918,73 @@
       <c r="AC88" s="2" t="inlineStr"/>
       <c r="AD88" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr"/>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr"/>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N89" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr"/>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -10990,7 +10998,7 @@
       <c r="U89" s="2" t="inlineStr"/>
       <c r="V89" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="W89" s="2" t="inlineStr">
@@ -11000,65 +11008,61 @@
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC89" s="2" t="inlineStr">
-        <is>
-          <t>91.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr"/>
       <c r="AD89" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr"/>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>沪A30260D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -11091,12 +11095,12 @@
       <c r="N90" s="2" t="inlineStr"/>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -11110,7 +11114,7 @@
       <c r="U90" s="2" t="inlineStr"/>
       <c r="V90" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="W90" s="2" t="inlineStr">
@@ -11146,77 +11150,73 @@
       <c r="AC90" s="2" t="inlineStr"/>
       <c r="AD90" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr"/>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr"/>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N91" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr"/>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -11230,7 +11230,7 @@
       <c r="U91" s="2" t="inlineStr"/>
       <c r="V91" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="W91" s="2" t="inlineStr">
@@ -11240,107 +11240,99 @@
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC91" s="2" t="inlineStr">
-        <is>
-          <t>92.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr"/>
       <c r="AD91" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr"/>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>93分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr"/>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N92" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr"/>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -11354,7 +11346,7 @@
       <c r="U92" s="2" t="inlineStr"/>
       <c r="V92" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="W92" s="2" t="inlineStr">
@@ -11364,65 +11356,61 @@
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC92" s="2" t="inlineStr">
-        <is>
-          <t>93.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr"/>
       <c r="AD92" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr"/>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>沪A51582D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -11455,12 +11443,12 @@
       <c r="N93" s="2" t="inlineStr"/>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -11474,7 +11462,7 @@
       <c r="U93" s="2" t="inlineStr"/>
       <c r="V93" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="W93" s="2" t="inlineStr">
@@ -11499,7 +11487,7 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
@@ -11510,77 +11498,73 @@
       <c r="AC93" s="2" t="inlineStr"/>
       <c r="AD93" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr"/>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>113分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr"/>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N94" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr"/>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -11594,7 +11578,7 @@
       <c r="U94" s="2" t="inlineStr"/>
       <c r="V94" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="W94" s="2" t="inlineStr">
@@ -11604,17 +11588,17 @@
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA94" s="2" t="inlineStr">
@@ -11624,87 +11608,79 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC94" s="2" t="inlineStr">
-        <is>
-          <t>113.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr"/>
       <c r="AD94" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr"/>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>沪A35683D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr"/>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N95" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr"/>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -11718,7 +11694,7 @@
       <c r="U95" s="2" t="inlineStr"/>
       <c r="V95" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="W95" s="2" t="inlineStr">
@@ -11728,17 +11704,17 @@
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA95" s="2" t="inlineStr">
@@ -11748,45 +11724,41 @@
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC95" s="2" t="inlineStr">
-        <is>
-          <t>91.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr"/>
       <c r="AD95" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr"/>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -11819,12 +11791,12 @@
       <c r="N96" s="2" t="inlineStr"/>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -11838,7 +11810,7 @@
       <c r="U96" s="2" t="inlineStr"/>
       <c r="V96" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="W96" s="2" t="inlineStr">
@@ -11868,13 +11840,17 @@
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC96" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
       <c r="AD96" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -11887,7 +11863,7 @@
       <c r="B97" s="2" t="inlineStr"/>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -11897,7 +11873,7 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
@@ -11907,39 +11883,35 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>106分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr"/>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N97" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr"/>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11958,7 +11930,7 @@
       <c r="U97" s="2" t="inlineStr"/>
       <c r="V97" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W97" s="2" t="inlineStr">
@@ -11968,17 +11940,17 @@
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA97" s="2" t="inlineStr">
@@ -11988,17 +11960,13 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC97" s="2" t="inlineStr">
-        <is>
-          <t>106.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr"/>
       <c r="AD97" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -12011,64 +11979,60 @@
       <c r="B98" s="2" t="inlineStr"/>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F98" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>97分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr"/>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N98" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr"/>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -12082,7 +12046,7 @@
       <c r="U98" s="2" t="inlineStr"/>
       <c r="V98" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="W98" s="2" t="inlineStr">
@@ -12092,37 +12056,33 @@
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z98" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC98" s="2" t="inlineStr">
-        <is>
-          <t>97.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr"/>
       <c r="AD98" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -12135,7 +12095,7 @@
       <c r="B99" s="2" t="inlineStr"/>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>沪A53062D</t>
+          <t>沪A30829D</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
@@ -12145,7 +12105,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -12155,44 +12115,40 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>94分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr"/>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N99" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr"/>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
@@ -12206,7 +12162,7 @@
       <c r="U99" s="2" t="inlineStr"/>
       <c r="V99" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W99" s="2" t="inlineStr">
@@ -12216,37 +12172,33 @@
       </c>
       <c r="X99" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y99" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z99" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA99" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC99" s="2" t="inlineStr">
-        <is>
-          <t>94.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr"/>
       <c r="AD99" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -12259,7 +12211,7 @@
       <c r="B100" s="2" t="inlineStr"/>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>沪A50235D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -12269,7 +12221,7 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>07:47</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
@@ -12289,12 +12241,12 @@
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>97分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr"/>
@@ -12311,12 +12263,12 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
@@ -12330,7 +12282,7 @@
       <c r="U100" s="2" t="inlineStr"/>
       <c r="V100" s="2" t="inlineStr">
         <is>
-          <t>07:47</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W100" s="2" t="inlineStr">
@@ -12355,7 +12307,7 @@
       </c>
       <c r="AA100" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB100" s="2" t="inlineStr">
@@ -12365,12 +12317,12 @@
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AD100" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -12383,7 +12335,7 @@
       <c r="B101" s="2" t="inlineStr"/>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A30260D</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
@@ -12393,7 +12345,7 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
@@ -12431,12 +12383,12 @@
       <c r="N101" s="2" t="inlineStr"/>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
@@ -12450,7 +12402,7 @@
       <c r="U101" s="2" t="inlineStr"/>
       <c r="V101" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W101" s="2" t="inlineStr">
@@ -12499,7 +12451,7 @@
       <c r="B102" s="2" t="inlineStr"/>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -12509,7 +12461,7 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
@@ -12519,40 +12471,44 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr"/>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N102" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
@@ -12566,7 +12522,7 @@
       <c r="U102" s="2" t="inlineStr"/>
       <c r="V102" s="2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W102" s="2" t="inlineStr">
@@ -12576,33 +12532,37 @@
       </c>
       <c r="X102" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z102" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA102" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC102" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AD102" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -12615,60 +12575,64 @@
       <c r="B103" s="2" t="inlineStr"/>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>沪A53893D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F103" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr"/>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N103" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -12682,7 +12646,7 @@
       <c r="U103" s="2" t="inlineStr"/>
       <c r="V103" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W103" s="2" t="inlineStr">
@@ -12692,33 +12656,37 @@
       </c>
       <c r="X103" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z103" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA103" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB103" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC103" s="2" t="inlineStr"/>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
       <c r="AD103" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -12731,7 +12699,7 @@
       <c r="B104" s="2" t="inlineStr"/>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A51582D</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -12741,7 +12709,7 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
@@ -12784,7 +12752,7 @@
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
@@ -12798,7 +12766,7 @@
       <c r="U104" s="2" t="inlineStr"/>
       <c r="V104" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W104" s="2" t="inlineStr">
@@ -12828,17 +12796,13 @@
       </c>
       <c r="AB104" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC104" s="2" t="inlineStr">
-        <is>
-          <t>91.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr"/>
       <c r="AD104" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -12851,60 +12815,64 @@
       <c r="B105" s="2" t="inlineStr"/>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
-        <is>
-          <t>08:20</t>
-        </is>
-      </c>
-      <c r="F105" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>113分钟</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr"/>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N105" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q105" s="2" t="inlineStr">
@@ -12918,7 +12886,7 @@
       <c r="U105" s="2" t="inlineStr"/>
       <c r="V105" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W105" s="2" t="inlineStr">
@@ -12928,33 +12896,37 @@
       </c>
       <c r="X105" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z105" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA105" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB105" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC105" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC105" s="2" t="inlineStr">
+        <is>
+          <t>113.0</t>
+        </is>
+      </c>
       <c r="AD105" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -12967,7 +12939,7 @@
       <c r="B106" s="2" t="inlineStr"/>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>沪A36930D</t>
+          <t>沪A35683D</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -12977,7 +12949,7 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
@@ -12987,40 +12959,44 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr"/>
       <c r="L106" s="2" t="inlineStr"/>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N106" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr">
@@ -13034,7 +13010,7 @@
       <c r="U106" s="2" t="inlineStr"/>
       <c r="V106" s="2" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W106" s="2" t="inlineStr">
@@ -13044,33 +13020,37 @@
       </c>
       <c r="X106" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y106" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z106" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA106" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB106" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB106" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC106" s="2" t="inlineStr"/>
+      <c r="AC106" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AD106" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -13083,7 +13063,7 @@
       <c r="B107" s="2" t="inlineStr"/>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
@@ -13093,7 +13073,7 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
@@ -13131,12 +13111,12 @@
       <c r="N107" s="2" t="inlineStr"/>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -13150,7 +13130,7 @@
       <c r="U107" s="2" t="inlineStr"/>
       <c r="V107" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W107" s="2" t="inlineStr">
@@ -13180,17 +13160,13 @@
       </c>
       <c r="AB107" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC107" s="2" t="inlineStr">
-        <is>
-          <t>92.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC107" s="2" t="inlineStr"/>
       <c r="AD107" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -13203,60 +13179,64 @@
       <c r="B108" s="2" t="inlineStr"/>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>沪A30829D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
-        <is>
-          <t>08:35</t>
-        </is>
-      </c>
-      <c r="F108" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>106分钟</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr"/>
       <c r="L108" s="2" t="inlineStr"/>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N108" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
@@ -13270,7 +13250,7 @@
       <c r="U108" s="2" t="inlineStr"/>
       <c r="V108" s="2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W108" s="2" t="inlineStr">
@@ -13280,17 +13260,17 @@
       </c>
       <c r="X108" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y108" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z108" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA108" s="2" t="inlineStr">
@@ -13300,13 +13280,17 @@
       </c>
       <c r="AB108" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC108" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC108" s="2" t="inlineStr">
+        <is>
+          <t>106.0</t>
+        </is>
+      </c>
       <c r="AD108" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -13319,7 +13303,7 @@
       <c r="B109" s="2" t="inlineStr"/>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>沪A30260D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
@@ -13329,7 +13313,7 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
@@ -13339,40 +13323,44 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr"/>
       <c r="L109" s="2" t="inlineStr"/>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N109" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="Q109" s="2" t="inlineStr">
@@ -13386,7 +13374,7 @@
       <c r="U109" s="2" t="inlineStr"/>
       <c r="V109" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W109" s="2" t="inlineStr">
@@ -13396,33 +13384,37 @@
       </c>
       <c r="X109" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y109" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z109" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA109" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB109" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC109" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC109" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
       <c r="AD109" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -13435,7 +13427,7 @@
       <c r="B110" s="2" t="inlineStr"/>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A53062D</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -13445,7 +13437,7 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
@@ -13455,40 +13447,44 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr"/>
       <c r="L110" s="2" t="inlineStr"/>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N110" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr">
@@ -13502,7 +13498,7 @@
       <c r="U110" s="2" t="inlineStr"/>
       <c r="V110" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W110" s="2" t="inlineStr">
@@ -13512,22 +13508,22 @@
       </c>
       <c r="X110" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y110" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z110" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA110" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB110" s="2" t="inlineStr">
@@ -13537,12 +13533,12 @@
       </c>
       <c r="AC110" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AD110" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -13555,7 +13551,7 @@
       <c r="B111" s="2" t="inlineStr"/>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>沪A51582D</t>
+          <t>沪A50235D</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
@@ -13565,7 +13561,7 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>07:47</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
@@ -13575,40 +13571,44 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr"/>
       <c r="L111" s="2" t="inlineStr"/>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N111" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N111" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
@@ -13622,7 +13622,7 @@
       <c r="U111" s="2" t="inlineStr"/>
       <c r="V111" s="2" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>07:47</t>
         </is>
       </c>
       <c r="W111" s="2" t="inlineStr">
@@ -13632,17 +13632,17 @@
       </c>
       <c r="X111" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y111" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z111" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA111" s="2" t="inlineStr">
@@ -13652,13 +13652,17 @@
       </c>
       <c r="AB111" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC111" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC111" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
       <c r="AD111" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -13671,7 +13675,7 @@
       <c r="B112" s="2" t="inlineStr"/>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>沪A35683D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -13681,7 +13685,7 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
@@ -13724,7 +13728,7 @@
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
@@ -13738,7 +13742,7 @@
       <c r="U112" s="2" t="inlineStr"/>
       <c r="V112" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W112" s="2" t="inlineStr">
@@ -13763,22 +13767,18 @@
       </c>
       <c r="AA112" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB112" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC112" s="2" t="inlineStr">
-        <is>
-          <t>91.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC112" s="2" t="inlineStr"/>
       <c r="AD112" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -13791,7 +13791,7 @@
       <c r="B113" s="2" t="inlineStr"/>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
@@ -13801,7 +13801,7 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
@@ -13839,7 +13839,7 @@
       <c r="N113" s="2" t="inlineStr"/>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P113" s="2" t="inlineStr">
@@ -13858,7 +13858,7 @@
       <c r="U113" s="2" t="inlineStr"/>
       <c r="V113" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="W113" s="2" t="inlineStr">
@@ -13888,17 +13888,13 @@
       </c>
       <c r="AB113" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC113" s="2" t="inlineStr">
-        <is>
-          <t>113.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC113" s="2" t="inlineStr"/>
       <c r="AD113" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -13911,7 +13907,7 @@
       <c r="B114" s="2" t="inlineStr"/>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A53893D</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -13921,7 +13917,7 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
@@ -13959,7 +13955,7 @@
       <c r="N114" s="2" t="inlineStr"/>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P114" s="2" t="inlineStr">
@@ -13978,7 +13974,7 @@
       <c r="U114" s="2" t="inlineStr"/>
       <c r="V114" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W114" s="2" t="inlineStr">
@@ -14003,22 +13999,18 @@
       </c>
       <c r="AA114" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB114" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC114" s="2" t="inlineStr">
-        <is>
-          <t>97.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC114" s="2" t="inlineStr"/>
       <c r="AD114" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -14031,22 +14023,22 @@
       <c r="B115" s="2" t="inlineStr"/>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E115" s="2" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
-      <c r="F115" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
@@ -14079,12 +14071,12 @@
       <c r="N115" s="2" t="inlineStr"/>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="Q115" s="2" t="inlineStr">
@@ -14098,7 +14090,7 @@
       <c r="U115" s="2" t="inlineStr"/>
       <c r="V115" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W115" s="2" t="inlineStr">
@@ -14123,18 +14115,22 @@
       </c>
       <c r="AA115" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB115" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC115" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC115" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AD115" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -14147,7 +14143,7 @@
       <c r="B116" s="2" t="inlineStr"/>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -14157,7 +14153,7 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
@@ -14195,12 +14191,12 @@
       <c r="N116" s="2" t="inlineStr"/>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -14214,7 +14210,7 @@
       <c r="U116" s="2" t="inlineStr"/>
       <c r="V116" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="W116" s="2" t="inlineStr">
@@ -14239,22 +14235,18 @@
       </c>
       <c r="AA116" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB116" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC116" s="2" t="inlineStr">
-        <is>
-          <t>106.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC116" s="2" t="inlineStr"/>
       <c r="AD116" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -14267,22 +14259,22 @@
       <c r="B117" s="2" t="inlineStr"/>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>沪A50235D</t>
+          <t>沪A36930D</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E117" s="2" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
-      <c r="F117" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
@@ -14315,12 +14307,12 @@
       <c r="N117" s="2" t="inlineStr"/>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
@@ -14334,7 +14326,7 @@
       <c r="U117" s="2" t="inlineStr"/>
       <c r="V117" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="W117" s="2" t="inlineStr">
@@ -14359,22 +14351,18 @@
       </c>
       <c r="AA117" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB117" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC117" s="2" t="inlineStr">
-        <is>
-          <t>97.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC117" s="2" t="inlineStr"/>
       <c r="AD117" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -14387,22 +14375,22 @@
       <c r="B118" s="2" t="inlineStr"/>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E118" s="2" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="F118" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
@@ -14435,12 +14423,12 @@
       <c r="N118" s="2" t="inlineStr"/>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
@@ -14454,7 +14442,7 @@
       <c r="U118" s="2" t="inlineStr"/>
       <c r="V118" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W118" s="2" t="inlineStr">
@@ -14479,18 +14467,22 @@
       </c>
       <c r="AA118" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB118" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC118" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC118" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AD118" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -14503,22 +14495,22 @@
       <c r="B119" s="2" t="inlineStr"/>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A30829D</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E119" s="2" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="F119" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
@@ -14556,7 +14548,7 @@
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="Q119" s="2" t="inlineStr">
@@ -14570,7 +14562,7 @@
       <c r="U119" s="2" t="inlineStr"/>
       <c r="V119" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="W119" s="2" t="inlineStr">
@@ -14595,7 +14587,7 @@
       </c>
       <c r="AA119" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB119" s="2" t="inlineStr">
@@ -14619,7 +14611,7 @@
       <c r="B120" s="2" t="inlineStr"/>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A30260D</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
@@ -14629,7 +14621,7 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
@@ -14667,12 +14659,12 @@
       <c r="N120" s="2" t="inlineStr"/>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q120" s="2" t="inlineStr">
@@ -14686,7 +14678,7 @@
       <c r="U120" s="2" t="inlineStr"/>
       <c r="V120" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W120" s="2" t="inlineStr">
@@ -14711,22 +14703,18 @@
       </c>
       <c r="AA120" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB120" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC120" s="2" t="inlineStr">
-        <is>
-          <t>91.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC120" s="2" t="inlineStr"/>
       <c r="AD120" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -14739,7 +14727,7 @@
       <c r="B121" s="2" t="inlineStr"/>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>沪A30829D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
@@ -14749,7 +14737,7 @@
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
@@ -14787,12 +14775,12 @@
       <c r="N121" s="2" t="inlineStr"/>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="Q121" s="2" t="inlineStr">
@@ -14806,7 +14794,7 @@
       <c r="U121" s="2" t="inlineStr"/>
       <c r="V121" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W121" s="2" t="inlineStr">
@@ -14831,18 +14819,22 @@
       </c>
       <c r="AA121" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB121" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC121" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC121" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
       <c r="AD121" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -14855,7 +14847,7 @@
       <c r="B122" s="2" t="inlineStr"/>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A51582D</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
@@ -14865,7 +14857,7 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
@@ -14908,7 +14900,7 @@
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="Q122" s="2" t="inlineStr">
@@ -14922,7 +14914,7 @@
       <c r="U122" s="2" t="inlineStr"/>
       <c r="V122" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="W122" s="2" t="inlineStr">
@@ -14952,17 +14944,13 @@
       </c>
       <c r="AB122" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC122" s="2" t="inlineStr">
-        <is>
-          <t>92.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC122" s="2" t="inlineStr"/>
       <c r="AD122" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -14975,22 +14963,22 @@
       <c r="B123" s="2" t="inlineStr"/>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A35683D</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E123" s="2" t="inlineStr">
-        <is>
-          <t>10:35</t>
-        </is>
-      </c>
-      <c r="F123" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
@@ -15023,12 +15011,12 @@
       <c r="N123" s="2" t="inlineStr"/>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="Q123" s="2" t="inlineStr">
@@ -15042,7 +15030,7 @@
       <c r="U123" s="2" t="inlineStr"/>
       <c r="V123" s="2" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W123" s="2" t="inlineStr">
@@ -15077,12 +15065,12 @@
       </c>
       <c r="AC123" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AD123" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -15095,7 +15083,7 @@
       <c r="B124" s="2" t="inlineStr"/>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>沪A35683D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
@@ -15105,7 +15093,7 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
@@ -15148,7 +15136,7 @@
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q124" s="2" t="inlineStr">
@@ -15162,7 +15150,7 @@
       <c r="U124" s="2" t="inlineStr"/>
       <c r="V124" s="2" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W124" s="2" t="inlineStr">
@@ -15187,7 +15175,7 @@
       </c>
       <c r="AA124" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB124" s="2" t="inlineStr">
@@ -15197,12 +15185,12 @@
       </c>
       <c r="AC124" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>113.0</t>
         </is>
       </c>
       <c r="AD124" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -15215,7 +15203,7 @@
       <c r="B125" s="2" t="inlineStr"/>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>沪A51582D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
@@ -15225,7 +15213,7 @@
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
@@ -15263,12 +15251,12 @@
       <c r="N125" s="2" t="inlineStr"/>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="Q125" s="2" t="inlineStr">
@@ -15282,7 +15270,7 @@
       <c r="U125" s="2" t="inlineStr"/>
       <c r="V125" s="2" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="W125" s="2" t="inlineStr">
@@ -15312,13 +15300,17 @@
       </c>
       <c r="AB125" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC125" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC125" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
       <c r="AD125" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -15336,17 +15328,17 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E126" s="2" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
-      <c r="F126" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
@@ -15384,7 +15376,7 @@
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="Q126" s="2" t="inlineStr">
@@ -15398,7 +15390,7 @@
       <c r="U126" s="2" t="inlineStr"/>
       <c r="V126" s="2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="W126" s="2" t="inlineStr">
@@ -15435,6 +15427,2138 @@
       <c r="AD126" s="2" t="inlineStr">
         <is>
           <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr"/>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr"/>
+      <c r="L127" s="2" t="inlineStr"/>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N127" s="2" t="inlineStr"/>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P127" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="Q127" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R127" s="2" t="inlineStr"/>
+      <c r="S127" s="2" t="inlineStr"/>
+      <c r="T127" s="2" t="inlineStr"/>
+      <c r="U127" s="2" t="inlineStr"/>
+      <c r="V127" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W127" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X127" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y127" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z127" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA127" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB127" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC127" s="2" t="inlineStr">
+        <is>
+          <t>106.0</t>
+        </is>
+      </c>
+      <c r="AD127" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr"/>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="inlineStr"/>
+      <c r="L128" s="2" t="inlineStr"/>
+      <c r="M128" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N128" s="2" t="inlineStr"/>
+      <c r="O128" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P128" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="Q128" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R128" s="2" t="inlineStr"/>
+      <c r="S128" s="2" t="inlineStr"/>
+      <c r="T128" s="2" t="inlineStr"/>
+      <c r="U128" s="2" t="inlineStr"/>
+      <c r="V128" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="W128" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X128" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y128" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z128" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA128" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB128" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC128" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="AD128" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr"/>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K129" s="2" t="inlineStr"/>
+      <c r="L129" s="2" t="inlineStr"/>
+      <c r="M129" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N129" s="2" t="inlineStr"/>
+      <c r="O129" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P129" s="2" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="Q129" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R129" s="2" t="inlineStr"/>
+      <c r="S129" s="2" t="inlineStr"/>
+      <c r="T129" s="2" t="inlineStr"/>
+      <c r="U129" s="2" t="inlineStr"/>
+      <c r="V129" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="W129" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X129" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y129" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z129" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA129" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB129" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC129" s="2" t="inlineStr"/>
+      <c r="AD129" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr"/>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="inlineStr"/>
+      <c r="L130" s="2" t="inlineStr"/>
+      <c r="M130" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N130" s="2" t="inlineStr"/>
+      <c r="O130" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P130" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="Q130" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R130" s="2" t="inlineStr"/>
+      <c r="S130" s="2" t="inlineStr"/>
+      <c r="T130" s="2" t="inlineStr"/>
+      <c r="U130" s="2" t="inlineStr"/>
+      <c r="V130" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="W130" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X130" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y130" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z130" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA130" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB130" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC130" s="2" t="inlineStr"/>
+      <c r="AD130" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr"/>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="inlineStr"/>
+      <c r="L131" s="2" t="inlineStr"/>
+      <c r="M131" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N131" s="2" t="inlineStr"/>
+      <c r="O131" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P131" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="Q131" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R131" s="2" t="inlineStr"/>
+      <c r="S131" s="2" t="inlineStr"/>
+      <c r="T131" s="2" t="inlineStr"/>
+      <c r="U131" s="2" t="inlineStr"/>
+      <c r="V131" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="W131" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X131" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y131" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z131" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA131" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB131" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC131" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AD131" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr"/>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>沪A30829D</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr"/>
+      <c r="L132" s="2" t="inlineStr"/>
+      <c r="M132" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N132" s="2" t="inlineStr"/>
+      <c r="O132" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P132" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="Q132" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R132" s="2" t="inlineStr"/>
+      <c r="S132" s="2" t="inlineStr"/>
+      <c r="T132" s="2" t="inlineStr"/>
+      <c r="U132" s="2" t="inlineStr"/>
+      <c r="V132" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="W132" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X132" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y132" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z132" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA132" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB132" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC132" s="2" t="inlineStr"/>
+      <c r="AD132" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr"/>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="inlineStr"/>
+      <c r="L133" s="2" t="inlineStr"/>
+      <c r="M133" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N133" s="2" t="inlineStr"/>
+      <c r="O133" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P133" s="2" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="Q133" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R133" s="2" t="inlineStr"/>
+      <c r="S133" s="2" t="inlineStr"/>
+      <c r="T133" s="2" t="inlineStr"/>
+      <c r="U133" s="2" t="inlineStr"/>
+      <c r="V133" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="W133" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X133" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y133" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z133" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA133" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB133" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC133" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AD133" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr"/>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr"/>
+      <c r="L134" s="2" t="inlineStr"/>
+      <c r="M134" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N134" s="2" t="inlineStr"/>
+      <c r="O134" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P134" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="Q134" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R134" s="2" t="inlineStr"/>
+      <c r="S134" s="2" t="inlineStr"/>
+      <c r="T134" s="2" t="inlineStr"/>
+      <c r="U134" s="2" t="inlineStr"/>
+      <c r="V134" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="W134" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X134" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y134" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z134" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA134" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB134" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC134" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AD134" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr"/>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>沪A35683D</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K135" s="2" t="inlineStr"/>
+      <c r="L135" s="2" t="inlineStr"/>
+      <c r="M135" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N135" s="2" t="inlineStr"/>
+      <c r="O135" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P135" s="2" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="Q135" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R135" s="2" t="inlineStr"/>
+      <c r="S135" s="2" t="inlineStr"/>
+      <c r="T135" s="2" t="inlineStr"/>
+      <c r="U135" s="2" t="inlineStr"/>
+      <c r="V135" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="W135" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X135" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y135" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z135" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA135" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB135" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC135" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AD135" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr"/>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>沪A51582D</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr"/>
+      <c r="L136" s="2" t="inlineStr"/>
+      <c r="M136" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N136" s="2" t="inlineStr"/>
+      <c r="O136" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P136" s="2" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="Q136" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R136" s="2" t="inlineStr"/>
+      <c r="S136" s="2" t="inlineStr"/>
+      <c r="T136" s="2" t="inlineStr"/>
+      <c r="U136" s="2" t="inlineStr"/>
+      <c r="V136" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="W136" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X136" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y136" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z136" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA136" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB136" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC136" s="2" t="inlineStr"/>
+      <c r="AD136" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr"/>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr"/>
+      <c r="L137" s="2" t="inlineStr"/>
+      <c r="M137" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N137" s="2" t="inlineStr"/>
+      <c r="O137" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P137" s="2" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="Q137" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R137" s="2" t="inlineStr"/>
+      <c r="S137" s="2" t="inlineStr"/>
+      <c r="T137" s="2" t="inlineStr"/>
+      <c r="U137" s="2" t="inlineStr"/>
+      <c r="V137" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="W137" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X137" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y137" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z137" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA137" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB137" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC137" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="AD137" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr"/>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr"/>
+      <c r="L138" s="2" t="inlineStr"/>
+      <c r="M138" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N138" s="2" t="inlineStr"/>
+      <c r="O138" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P138" s="2" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="Q138" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R138" s="2" t="inlineStr"/>
+      <c r="S138" s="2" t="inlineStr"/>
+      <c r="T138" s="2" t="inlineStr"/>
+      <c r="U138" s="2" t="inlineStr"/>
+      <c r="V138" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="W138" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X138" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y138" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z138" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA138" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB138" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC138" s="2" t="inlineStr"/>
+      <c r="AD138" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr"/>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="inlineStr"/>
+      <c r="L139" s="2" t="inlineStr"/>
+      <c r="M139" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N139" s="2" t="inlineStr"/>
+      <c r="O139" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P139" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="Q139" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R139" s="2" t="inlineStr"/>
+      <c r="S139" s="2" t="inlineStr"/>
+      <c r="T139" s="2" t="inlineStr"/>
+      <c r="U139" s="2" t="inlineStr"/>
+      <c r="V139" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="W139" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X139" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y139" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z139" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA139" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB139" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC139" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="AD139" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr"/>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="inlineStr"/>
+      <c r="L140" s="2" t="inlineStr"/>
+      <c r="M140" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N140" s="2" t="inlineStr"/>
+      <c r="O140" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P140" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="Q140" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R140" s="2" t="inlineStr"/>
+      <c r="S140" s="2" t="inlineStr"/>
+      <c r="T140" s="2" t="inlineStr"/>
+      <c r="U140" s="2" t="inlineStr"/>
+      <c r="V140" s="2" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="W140" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X140" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y140" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z140" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA140" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB140" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC140" s="2" t="inlineStr">
+        <is>
+          <t>106.0</t>
+        </is>
+      </c>
+      <c r="AD140" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr"/>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K141" s="2" t="inlineStr"/>
+      <c r="L141" s="2" t="inlineStr"/>
+      <c r="M141" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N141" s="2" t="inlineStr"/>
+      <c r="O141" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P141" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="Q141" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R141" s="2" t="inlineStr"/>
+      <c r="S141" s="2" t="inlineStr"/>
+      <c r="T141" s="2" t="inlineStr"/>
+      <c r="U141" s="2" t="inlineStr"/>
+      <c r="V141" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="W141" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X141" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y141" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z141" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA141" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB141" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC141" s="2" t="inlineStr"/>
+      <c r="AD141" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr"/>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K142" s="2" t="inlineStr"/>
+      <c r="L142" s="2" t="inlineStr"/>
+      <c r="M142" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N142" s="2" t="inlineStr"/>
+      <c r="O142" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P142" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="Q142" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R142" s="2" t="inlineStr"/>
+      <c r="S142" s="2" t="inlineStr"/>
+      <c r="T142" s="2" t="inlineStr"/>
+      <c r="U142" s="2" t="inlineStr"/>
+      <c r="V142" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="W142" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X142" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y142" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z142" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA142" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB142" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC142" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AD142" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr"/>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>沪A30829D</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K143" s="2" t="inlineStr"/>
+      <c r="L143" s="2" t="inlineStr"/>
+      <c r="M143" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N143" s="2" t="inlineStr"/>
+      <c r="O143" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P143" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="Q143" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R143" s="2" t="inlineStr"/>
+      <c r="S143" s="2" t="inlineStr"/>
+      <c r="T143" s="2" t="inlineStr"/>
+      <c r="U143" s="2" t="inlineStr"/>
+      <c r="V143" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="W143" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X143" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y143" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z143" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA143" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB143" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC143" s="2" t="inlineStr"/>
+      <c r="AD143" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr"/>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K144" s="2" t="inlineStr"/>
+      <c r="L144" s="2" t="inlineStr"/>
+      <c r="M144" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N144" s="2" t="inlineStr"/>
+      <c r="O144" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P144" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="Q144" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R144" s="2" t="inlineStr"/>
+      <c r="S144" s="2" t="inlineStr"/>
+      <c r="T144" s="2" t="inlineStr"/>
+      <c r="U144" s="2" t="inlineStr"/>
+      <c r="V144" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="W144" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X144" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y144" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z144" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA144" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB144" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC144" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AD144" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-28-operations.xlsx
+++ b/data/export/2026-10-28-operations.xlsx
@@ -1668,7 +1668,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -5000,7 +5000,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5236,7 +5236,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5944,7 +5944,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6176,7 +6176,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -8200,7 +8200,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -9620,7 +9620,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9856,7 +9856,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -11280,7 +11280,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -11516,7 +11516,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -11872,7 +11872,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -11988,7 +11988,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -14352,7 +14352,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
@@ -17380,7 +17380,7 @@
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q143" s="2" t="inlineStr">
@@ -22616,7 +22616,7 @@
       </c>
       <c r="P188" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q188" s="2" t="inlineStr">
@@ -24364,7 +24364,7 @@
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q203" s="2" t="inlineStr">
@@ -24952,7 +24952,7 @@
       </c>
       <c r="P208" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q208" s="2" t="inlineStr">
@@ -25436,7 +25436,7 @@
       </c>
       <c r="P212" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q212" s="2" t="inlineStr">
@@ -26292,7 +26292,7 @@
       </c>
       <c r="P219" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q219" s="2" t="inlineStr">
@@ -27228,7 +27228,7 @@
       </c>
       <c r="P227" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q227" s="2" t="inlineStr">
@@ -27700,7 +27700,7 @@
       </c>
       <c r="P231" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q231" s="2" t="inlineStr">
@@ -28296,7 +28296,7 @@
       </c>
       <c r="P236" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q236" s="2" t="inlineStr">
@@ -31720,7 +31720,7 @@
       </c>
       <c r="P265" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q265" s="2" t="inlineStr">
@@ -32076,7 +32076,7 @@
       </c>
       <c r="P268" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q268" s="2" t="inlineStr">
@@ -32552,7 +32552,7 @@
       </c>
       <c r="P272" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q272" s="2" t="inlineStr">
@@ -33848,7 +33848,7 @@
       </c>
       <c r="P283" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q283" s="2" t="inlineStr">
@@ -34084,7 +34084,7 @@
       </c>
       <c r="P285" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q285" s="2" t="inlineStr">
@@ -34560,7 +34560,7 @@
       </c>
       <c r="P289" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q289" s="2" t="inlineStr">
@@ -35856,7 +35856,7 @@
       </c>
       <c r="P300" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q300" s="2" t="inlineStr">
@@ -36092,7 +36092,7 @@
       </c>
       <c r="P302" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q302" s="2" t="inlineStr">
@@ -36332,7 +36332,7 @@
       </c>
       <c r="P304" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q304" s="2" t="inlineStr">
@@ -36564,7 +36564,7 @@
       </c>
       <c r="P306" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q306" s="2" t="inlineStr">
@@ -36680,7 +36680,7 @@
       </c>
       <c r="P307" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q307" s="2" t="inlineStr">
@@ -36800,7 +36800,7 @@
       </c>
       <c r="P308" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q308" s="2" t="inlineStr">

--- a/data/export/2026-10-28-operations.xlsx
+++ b/data/export/2026-10-28-operations.xlsx
@@ -26292,7 +26292,7 @@
       </c>
       <c r="P219" s="2" t="inlineStr">
         <is>
-          <t>21:11</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q219" s="2" t="inlineStr">
@@ -28296,7 +28296,7 @@
       </c>
       <c r="P236" s="2" t="inlineStr">
         <is>
-          <t>21:11</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q236" s="2" t="inlineStr">
@@ -32552,7 +32552,7 @@
       </c>
       <c r="P272" s="2" t="inlineStr">
         <is>
-          <t>21:11</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q272" s="2" t="inlineStr">
@@ -34560,7 +34560,7 @@
       </c>
       <c r="P289" s="2" t="inlineStr">
         <is>
-          <t>21:11</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q289" s="2" t="inlineStr">
@@ -36332,7 +36332,7 @@
       </c>
       <c r="P304" s="2" t="inlineStr">
         <is>
-          <t>21:11</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q304" s="2" t="inlineStr">
@@ -36800,7 +36800,7 @@
       </c>
       <c r="P308" s="2" t="inlineStr">
         <is>
-          <t>21:11</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q308" s="2" t="inlineStr">
